--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -376,7 +376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="8.710000000000001" customWidth="1" style="7" min="1" max="1"/>
@@ -1039,18 +1039,396 @@
       <c r="J19" s="1" t="n"/>
       <c r="K19" s="1" t="n"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="7"/>
-    <row r="22" ht="15.75" customHeight="1" s="7"/>
-    <row r="23" ht="15.75" customHeight="1" s="7"/>
-    <row r="24" ht="15.75" customHeight="1" s="7"/>
-    <row r="25" ht="15.75" customHeight="1" s="7"/>
-    <row r="26" ht="15.75" customHeight="1" s="7"/>
-    <row r="27" ht="15.75" customHeight="1" s="7"/>
-    <row r="28" ht="15.75" customHeight="1" s="7"/>
-    <row r="29" ht="15.75" customHeight="1" s="7"/>
-    <row r="30" ht="15.75" customHeight="1" s="7"/>
-    <row r="31" ht="15.75" customHeight="1" s="7"/>
-    <row r="32" ht="15.75" customHeight="1" s="7"/>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LU0552029661</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMUNDI FUNDS LATIN AMERICA EQUITY - G EUR (C)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Amundi</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Azionari America Latina</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="7">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LU1213835942</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - Latin America Fund A-ACC-EUR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Azionari America Latina</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="7">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LU0309468808</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nordea-1 Latin American Eq BP Acc</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nordea</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Azionari America Latina</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="7">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LU0522352862</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - JPM Latin America Equity D (acc) - EUR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Azionari America Latina</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="7">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LU0326425351</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BlackRock Global Funds - World Mining Hedged E2 EUR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Azionari Materie Prime</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="7">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LU0172157363</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BGF World Mining Euro E</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Azionari Materie Prime</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="7">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LU0106817157</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Schroder ISF Emerg Eur A Acc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Schroders</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Azionari Europa Emergente</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="7">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LU0326422507</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BlackRock Global Funds - World Energy Hedged E2 EUR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Azionari Energia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="7">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LU0171304552</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BGF World Energy Euro E</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Azionari Energia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="7">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LU0056052961</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Candriam Equities L Emerging Markets C EUR Acc</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Candriam</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Azionari Mercati Emergenti</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="7">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LU1882448316</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Amundi Fds - Emerging Europe Middle East and Africa - cl E2 Eur C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Amundi</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Azionari Europa/Africa/ME</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="7">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LU0303816028</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - Emerging Europe, Middle East and Africa A Euro</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Azionari Europa/Africa/ME</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="7">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LU0307839646</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - Emerging Markets A Euro</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Azionari Mercati Emergenti</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
     <row r="33" ht="15.75" customHeight="1" s="7"/>
     <row r="34" ht="15.75" customHeight="1" s="7"/>
     <row r="35" ht="15.75" customHeight="1" s="7"/>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.710000000000001" customWidth="1" style="7" min="1" max="1"/>
@@ -1936,38 +1936,1126 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="8"/>
-    <row r="34" ht="15.75" customHeight="1" s="8"/>
-    <row r="35" ht="15.75" customHeight="1" s="8"/>
-    <row r="36" ht="15.75" customHeight="1" s="8"/>
-    <row r="37" ht="15.75" customHeight="1" s="8"/>
-    <row r="38" ht="15.75" customHeight="1" s="8"/>
-    <row r="39" ht="15.75" customHeight="1" s="8"/>
-    <row r="40" ht="15.75" customHeight="1" s="8"/>
-    <row r="41" ht="15.75" customHeight="1" s="8"/>
-    <row r="42" ht="15.75" customHeight="1" s="8"/>
-    <row r="43" ht="15.75" customHeight="1" s="8"/>
-    <row r="44" ht="15.75" customHeight="1" s="8"/>
-    <row r="45" ht="15.75" customHeight="1" s="8"/>
-    <row r="46" ht="15.75" customHeight="1" s="8"/>
-    <row r="47" ht="15.75" customHeight="1" s="8"/>
-    <row r="48" ht="15.75" customHeight="1" s="8"/>
-    <row r="49" ht="15.75" customHeight="1" s="8"/>
-    <row r="50" ht="15.75" customHeight="1" s="8"/>
-    <row r="51" ht="15.75" customHeight="1" s="8"/>
-    <row r="52" ht="15.75" customHeight="1" s="8"/>
-    <row r="53" ht="15.75" customHeight="1" s="8"/>
-    <row r="54" ht="15.75" customHeight="1" s="8"/>
-    <row r="55" ht="15.75" customHeight="1" s="8"/>
-    <row r="56" ht="15.75" customHeight="1" s="8"/>
-    <row r="57" ht="15.75" customHeight="1" s="8"/>
-    <row r="58" ht="15.75" customHeight="1" s="8"/>
-    <row r="59" ht="15.75" customHeight="1" s="8"/>
-    <row r="60" ht="15.75" customHeight="1" s="8"/>
-    <row r="61" ht="15.75" customHeight="1" s="8"/>
-    <row r="62" ht="15.75" customHeight="1" s="8"/>
-    <row r="63" ht="15.75" customHeight="1" s="8"/>
-    <row r="64" ht="15.75" customHeight="1" s="8"/>
+    <row r="33" ht="15.75" customHeight="1" s="8">
+      <c r="A33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LU0114720955</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - Global Health Care A EUR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Azionari Salute/Pharma</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="8">
+      <c r="A34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LU0329630130</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Global Healthcare A EUR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Azionari Salute/Pharma</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="8">
+      <c r="A35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LU0329455071</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Candriam Equities L Oncology Impact C EUR</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Candriam</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Azionari Salute/Pharma</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="8">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LU0473185139</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - Global Financial Services A EUR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Azionari Finanziari</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="8">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LU0210527791</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Europe Equity A EUR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Azionari Finanziari</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="8">
+      <c r="A38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LU0363470070</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DWS Invest Global Infrastructure LC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DWS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Azionari Infrastrutture</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="8">
+      <c r="A39" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LU0187079347</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Invesco Global Consumer Trends A EUR</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Invesco</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Azionari Consumi/Lusso</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="8">
+      <c r="A40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LU0640476718</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - Sustainable Consumer Brands A EUR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Azionari Consumi/Lusso</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="8">
+      <c r="A41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LU0210534433</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - US Growth A EUR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Azionari USA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="8">
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LU0069450822</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - America Fund A EUR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Azionari USA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="8">
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LU1213835603</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Amundi Fds - Pioneer US Equity Fundamental Growth A EUR C</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Amundi</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Azionari USA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="8">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LU0210073469</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Europe Dynamic A EUR</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Azionari Europa</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="8">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LU0346388373</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Nordea 1 - European Stars Equity BP EUR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Nordea</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Azionari Europa</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="8">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LU0119750205</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - European Growth A EUR</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Azionari Europa</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="8">
+      <c r="A47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LU0161332480</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Japan Equity A EUR</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Azionari Giappone</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" s="8">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LU0413542167</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Schroders ISF Japanese Equity A EUR Hdg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Schroders</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Azionari Giappone</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" s="8">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LU0210526066</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Pacific Equity A EUR</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Azionari Asia Pacifico</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="8">
+      <c r="A50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LU0048597586</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - Asia Focus A EUR</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Azionari Asia Pacifico</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" s="8">
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LU0210526579</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - China A EUR</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Azionari Cina</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" s="8">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LU1213836676</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Amundi Fds - China Equity A EUR C</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Amundi</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Azionari Cina</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" s="8">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LU0333810181</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - India A EUR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Azionari India</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="8">
+      <c r="A54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LU0210534516</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Global Select Equity A EUR</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Azionari Globali</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" s="8">
+      <c r="A55" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LU0605515377</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Nordea 1 - Global Stars Equity BP EUR</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Nordea</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Azionari Globali</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="8">
+      <c r="A56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LU0210531934</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Europe High Yield Bond A EUR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Obbligazionari High Yield</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="8">
+      <c r="A57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LU0159052710</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Candriam Bonds Euro High Yield C EUR</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Candriam</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Obbligazionari High Yield</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" s="8">
+      <c r="A58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LU0155953517</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Fidelity Funds - European High Yield A EUR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Fidelity</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Obbligazionari High Yield</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" s="8">
+      <c r="A59" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LU0522351971</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Emerging Markets Debt A EUR Hdg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Obbligazionari Mercati Emergenti</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" s="8">
+      <c r="A60" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LU0238205289</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Amundi Fds - Emerging Markets Bond A EUR C</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Amundi</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Obbligazionari Mercati Emergenti</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" s="8">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LU0210531850</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Global Bond Opportunities A EUR Hdg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Obbligazionari Globali</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="8">
+      <c r="A62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LU0168060498</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Nordea 1 - European Covered Bond BP EUR</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nordea</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Obbligazionari Globali</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="8">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FR0010510800</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Amundi Fds - Euro Government Bond A EUR C</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Amundi</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Monetari Euro</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" s="8">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LU0568621618</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Euro Government Liquidity A EUR</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>JPMorgan</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Monetari Euro</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
     <row r="65" ht="15.75" customHeight="1" s="8"/>
     <row r="66" ht="15.75" customHeight="1" s="8"/>
     <row r="67" ht="15.75" customHeight="1" s="8"/>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +56,11 @@
         <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF6600"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -69,11 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,13 +535,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>288.73</v>
+        <v>291.67</v>
       </c>
       <c r="H2" t="n">
-        <v>284.722</v>
+        <v>286.101</v>
       </c>
       <c r="I2" t="n">
-        <v>57.77</v>
+        <v>61.92</v>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
@@ -544,7 +550,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -578,13 +584,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>355.95</v>
+        <v>369.06</v>
       </c>
       <c r="H3" t="n">
-        <v>339.8735</v>
+        <v>346.281</v>
       </c>
       <c r="I3" t="n">
-        <v>58.1</v>
+        <v>63.63</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -593,7 +599,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -627,13 +633,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>304.21</v>
+        <v>315.41</v>
       </c>
       <c r="H4" t="n">
-        <v>290.546</v>
+        <v>295.988</v>
       </c>
       <c r="I4" t="n">
-        <v>60.28</v>
+        <v>65.02</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -642,7 +648,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -676,13 +682,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18.59</v>
+        <v>18.95</v>
       </c>
       <c r="H5" t="n">
-        <v>18.0185</v>
+        <v>18.301</v>
       </c>
       <c r="I5" t="n">
-        <v>60.98</v>
+        <v>65.36</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -691,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -725,13 +731,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20.04</v>
+        <v>19.99</v>
       </c>
       <c r="H6" t="n">
-        <v>20.131</v>
+        <v>20.076</v>
       </c>
       <c r="I6" t="n">
-        <v>45.89</v>
+        <v>42.22</v>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
@@ -740,22 +746,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LU1499628912</t>
+          <t>LU2357810188</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amundi S.F. - Diversified Short-Term Bond Select E EUR ND</t>
+          <t>Amundi S.F. - Diversified Short-Term Bond Select A EUR AD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -774,22 +780,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5.95</v>
+        <v>51.1</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9493</v>
+        <v>51.951</v>
       </c>
       <c r="I7" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+        <v>6.63</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -799,22 +805,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LU2357810428</t>
+          <t>LU1046235815</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amundi S.F. - Diversified Short-Term Bond Select F EUR C</t>
+          <t>Schroder ISF Strategic Credit B EUR Hedged Acc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Schroders</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Obbligazionari Breve Termine</t>
+          <t>Obbligazionari Corporate</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -823,22 +829,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5.7</v>
+        <v>125.74</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6986</v>
+        <v>125.5842</v>
       </c>
       <c r="I8" t="n">
-        <v>65.36</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+        <v>79.52</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -848,12 +854,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LU1046235815</t>
+          <t>LU1046236037</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Schroder ISF Strategic Credit B EUR Hedged Acc</t>
+          <t>Schroder ISF Strategic Credit A EUR Hedged Inc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -872,13 +878,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>125.68</v>
+        <v>94.98</v>
       </c>
       <c r="H9" t="n">
-        <v>125.4802</v>
+        <v>94.85299999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>76.87</v>
+        <v>82.16</v>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
@@ -887,7 +893,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -897,22 +903,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU1046236037</t>
+          <t>IT0004782758</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Schroder ISF Strategic Credit A EUR Hedged Inc</t>
+          <t>Eurizon Obbligazioni Euro Breve Term A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Schroders</t>
+          <t>Eurizon</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Obbligazionari Corporate</t>
+          <t>Obbligazionari Euro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -921,22 +927,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>94.94</v>
+        <v>17.13</v>
       </c>
       <c r="H10" t="n">
-        <v>94.7679</v>
+        <v>17.1214</v>
       </c>
       <c r="I10" t="n">
-        <v>80.15000000000001</v>
-      </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -946,22 +952,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IT0004782758</t>
+          <t>LU0430494962</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eurizon Obbligazioni Euro Breve Term A</t>
+          <t>JPM Global Short Duration Bond Fund A (acc) EUR hedged</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Eurizon</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Obbligazionari Euro</t>
+          <t>Obbligazionari Breve Termine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -970,13 +976,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>17.13</v>
+        <v>7.68</v>
       </c>
       <c r="H11" t="n">
-        <v>17.1126</v>
+        <v>7.6715</v>
       </c>
       <c r="I11" t="n">
-        <v>69.59999999999999</v>
+        <v>68.19</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -985,7 +991,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -995,12 +1001,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LU0430494962</t>
+          <t>LU0408876448</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JPM Global Short Duration Bond Fund A (acc) EUR hedged</t>
+          <t>JPM Global Government Short Duration Bond A (acc) EUR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1010,7 +1016,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Obbligazionari Breve Termine</t>
+          <t>Obbligazionari Governativi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1019,22 +1025,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7.67</v>
+        <v>10.83</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6665</v>
+        <v>10.8215</v>
       </c>
       <c r="I12" t="n">
-        <v>58.11</v>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+        <v>74.66</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1044,22 +1050,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LU0408876448</t>
+          <t>LU1915690595</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JPM Global Government Short Duration Bond A (acc) EUR</t>
+          <t>Nordea 1 - Active Rates Opportunities Fund BP EUR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Nordea</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Obbligazionari Governativi</t>
+          <t>Obbligazionari Flessibili</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1068,13 +1074,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>10.83</v>
+        <v>123.08</v>
       </c>
       <c r="H13" t="n">
-        <v>10.814</v>
+        <v>122.852</v>
       </c>
       <c r="I13" t="n">
-        <v>74.66</v>
+        <v>62.65</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
@@ -1083,32 +1089,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LU1915690595</t>
+          <t>LU0165520114</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nordea 1 - Active Rates Opportunities Fund BP EUR</t>
+          <t>Candriam Bonds Global Inflation Short duration Classic C Acc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nordea</t>
+          <t>Candriam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Obbligazionari Flessibili</t>
+          <t>Obbligazionari Inflation Linked</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1117,13 +1123,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>123.03</v>
+        <v>149.61</v>
       </c>
       <c r="H14" t="n">
-        <v>122.7935</v>
+        <v>149.526</v>
       </c>
       <c r="I14" t="n">
-        <v>60.99</v>
+        <v>54.78</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1142,22 +1148,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LU0165520114</t>
+          <t>LU1213836080</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Candriam Bonds Global Inflation Short duration Classic C Acc</t>
+          <t>Fidelity Funds - Global Technology Fund A-ACC-EUR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Candriam</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Obbligazionari Inflation Linked</t>
+          <t>Azionari Tecnologia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1166,13 +1172,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>149.51</v>
+        <v>56.76</v>
       </c>
       <c r="H15" t="n">
-        <v>149.564</v>
+        <v>57.501</v>
       </c>
       <c r="I15" t="n">
-        <v>50.08</v>
+        <v>37.35</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
@@ -1181,32 +1187,32 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LU1213836080</t>
+          <t>IE000RHGM613</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Global Technology Fund A-ACC-EUR</t>
+          <t>Nbg Bm Nex Gen Spc Ecy EUR M Acc Unh</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>NBG Asset Management</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azionari Tecnologia</t>
+          <t>Azionari Tematici</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1215,13 +1221,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>58.21</v>
+        <v>22.51</v>
       </c>
       <c r="H16" t="n">
-        <v>57.989</v>
+        <v>22.271</v>
       </c>
       <c r="I16" t="n">
-        <v>49.44</v>
+        <v>52.57</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1230,32 +1236,32 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IE000RHGM613</t>
+          <t>LU2484078832</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nbg Bm Nex Gen Spc Ecy EUR M Acc Unh</t>
+          <t>Invesco Funds - Invesco Metaverse and AI Fund A Acc EUR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NBG Asset Management</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azionari Tematici</t>
+          <t>Azionari Tecnologia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1264,13 +1270,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>22.66</v>
+        <v>18.27</v>
       </c>
       <c r="H17" t="n">
-        <v>22.3985</v>
+        <v>18.1005</v>
       </c>
       <c r="I17" t="n">
-        <v>54.65</v>
+        <v>55.4</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1279,7 +1285,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1295,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LU2473541584</t>
+          <t>LU0115773425</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Invesco Metaverse and AI Fund E Acc EUR</t>
+          <t>FF - Global Technology Fund - E - ACC - Euro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1313,13 +1319,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>17.62</v>
+        <v>71.75</v>
       </c>
       <c r="H18" t="n">
-        <v>17.539</v>
+        <v>72.699</v>
       </c>
       <c r="I18" t="n">
-        <v>51.84</v>
+        <v>37.19</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
@@ -1328,22 +1334,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LU0115773425</t>
+          <t>LU1213835942</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FF - Global Technology Fund - E - ACC - Euro</t>
+          <t>Fidelity Funds - Latin America Fund A-ACC-EUR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1353,7 +1359,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azionari Tecnologia</t>
+          <t>Azionari America Latina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1362,13 +1368,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>73.59</v>
+        <v>15.17</v>
       </c>
       <c r="H19" t="n">
-        <v>73.3235</v>
+        <v>14.9555</v>
       </c>
       <c r="I19" t="n">
-        <v>49.29</v>
+        <v>63.25</v>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
@@ -1377,7 +1383,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1387,17 +1393,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LU0552029661</t>
+          <t>LU0309468808</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AMUNDI FUNDS LATIN AMERICA EQUITY - G EUR (C)</t>
+          <t>Nordea-1 Latin American Eq BP Acc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Nordea</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1411,22 +1417,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>125.59</v>
+        <v>20.1</v>
       </c>
       <c r="H20" t="n">
-        <v>121.514</v>
+        <v>19.7345</v>
       </c>
       <c r="I20" t="n">
-        <v>70.78</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+        <v>67.68000000000001</v>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1442,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LU1213835942</t>
+          <t>LU0522352862</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Latin America Fund A-ACC-EUR</t>
+          <t>JPMorgan Funds - JPM Latin America Equity D (acc) - EUR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1460,96 +1466,96 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>15.28</v>
+        <v>116.14</v>
       </c>
       <c r="H21" t="n">
-        <v>14.85</v>
+        <v>113.71</v>
       </c>
       <c r="I21" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+        <v>67.59</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LU0326424115</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BlackRock Global Funds - World Mining Fund A2 EUR Hedged</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Azionari Materie Prime</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.9335</v>
+      </c>
+      <c r="I22" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-02-24 15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LU0309468808</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nordea-1 Latin American Eq BP Acc</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nordea</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Azionari America Latina</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19.5485</v>
-      </c>
-      <c r="I22" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2</v>
-      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LU0522352862</t>
+          <t>LU0106817157</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - JPM Latin America Equity D (acc) - EUR</t>
+          <t>Schroder ISF Emerg Eur A Acc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Schroders</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azionari America Latina</t>
+          <t>Azionari Europa Emergente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1558,13 +1564,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>114.52</v>
+        <v>32.65</v>
       </c>
       <c r="H23" t="n">
-        <v>112.8455</v>
+        <v>32.5763</v>
       </c>
       <c r="I23" t="n">
-        <v>63.35</v>
+        <v>56.51</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -1573,81 +1579,81 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LU0326422176</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BlackRock Global Funds - World Energy Fund A2 EUR Hedged</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Azionari Energia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.2805</v>
+      </c>
+      <c r="I24" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-02-24 15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LU0326425351</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BlackRock Global Funds - World Mining Hedged E2 EUR</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Azionari Materie Prime</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="H24" t="n">
-        <v>7.191</v>
-      </c>
-      <c r="I24" t="n">
-        <v>56.56</v>
-      </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>3</v>
-      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LU0172157363</t>
+          <t>LU0056052961</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BGF World Mining Euro E</t>
+          <t>Candriam Equities L Emerging Markets C EUR Acc</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Candriam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azionari Materie Prime</t>
+          <t>Azionari Mercati Emergenti</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1655,6 +1661,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>1382.77</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1334.846</v>
+      </c>
+      <c r="I25" t="n">
+        <v>68.48</v>
+      </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -1662,7 +1677,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1672,22 +1687,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LU0106817157</t>
+          <t>IE00BGMHJH08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Schroder ISF Emerg Eur A Acc</t>
+          <t>Amundi Alternative Funds II PLC - Amundi Marathon Emerging Markets Bond Fund A EUR Acc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Schroders</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azionari Europa Emergente</t>
+          <t>Azionari Europa/Africa/ME</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1696,13 +1711,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>32.22</v>
+        <v>101.12</v>
       </c>
       <c r="H26" t="n">
-        <v>32.6857</v>
+        <v>33.9061</v>
       </c>
       <c r="I26" t="n">
-        <v>50.35</v>
+        <v>54.83</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -1711,7 +1726,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1736,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LU0326422507</t>
+          <t>LU0303816028</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BlackRock Global Funds - World Energy Hedged E2 EUR</t>
+          <t>Fidelity Funds - Emerging Europe, Middle East and Africa A Euro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azionari Energia</t>
+          <t>Azionari Europa/Africa/ME</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1745,47 +1760,47 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6.89</v>
+        <v>19.18</v>
       </c>
       <c r="H27" t="n">
-        <v>6.658</v>
+        <v>18.847</v>
       </c>
       <c r="I27" t="n">
-        <v>72.58</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+        <v>66</v>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LU0171304552</t>
+          <t>LU0307839646</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BGF World Energy Euro E</t>
+          <t>Fidelity Funds - Emerging Markets A Euro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azionari Energia</t>
+          <t>Azionari Mercati Emergenti</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1793,6 +1808,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G28" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="H28" t="n">
+        <v>21.5235</v>
+      </c>
+      <c r="I28" t="n">
+        <v>68.38</v>
+      </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -1800,32 +1824,32 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LU0056052961</t>
+          <t>LU0114720955</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Candriam Equities L Emerging Markets C EUR Acc</t>
+          <t>Fidelity Funds - Global Health Care A EUR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Candriam</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azionari Mercati Emergenti</t>
+          <t>Azionari Salute/Pharma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1834,13 +1858,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1348.95</v>
+        <v>62.45</v>
       </c>
       <c r="H29" t="n">
-        <v>1320.208</v>
+        <v>62.1505</v>
       </c>
       <c r="I29" t="n">
-        <v>62.9</v>
+        <v>50.07</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1849,7 +1873,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1859,22 +1883,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IE00BGMHJH08</t>
+          <t>LU0880062913</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Amundi Alternative Funds II PLC - Amundi Marathon Emerging Markets Bond Fund A EUR Acc</t>
+          <t>JPMorgan Funds - Global Healthcare Fund A (acc) - EUR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azionari Europa/Africa/ME</t>
+          <t>Azionari Salute/Pharma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1883,13 +1907,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>101.11</v>
+        <v>282.1</v>
       </c>
       <c r="H30" t="n">
-        <v>33.9061</v>
+        <v>281.0385</v>
       </c>
       <c r="I30" t="n">
-        <v>54.83</v>
+        <v>50.14</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -1898,22 +1922,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>2</v>
+      <c r="A31" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LU0303816028</t>
+          <t>LU1391767586</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Emerging Europe, Middle East and Africa A Euro</t>
+          <t>Fidelity Funds - Global Financial Services Fund A-Acc-EUR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1923,7 +1947,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azionari Europa/Africa/ME</t>
+          <t>Azionari Finanziari</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1932,13 +1956,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>18.86</v>
+        <v>25.03</v>
       </c>
       <c r="H31" t="n">
-        <v>18.7215</v>
+        <v>25.655</v>
       </c>
       <c r="I31" t="n">
-        <v>58.38</v>
+        <v>35.5</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -1947,7 +1971,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -1957,22 +1981,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LU0307839646</t>
+          <t>LU0210527791</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Emerging Markets A Euro</t>
+          <t>JPMorgan Funds - Europe Equity A EUR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azionari Mercati Emergenti</t>
+          <t>Azionari Finanziari</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1981,37 +2005,37 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>22.03</v>
+        <v>32.43000030517578</v>
       </c>
       <c r="H32" t="n">
-        <v>21.286</v>
+        <v>31.8945</v>
       </c>
       <c r="I32" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+        <v>68.95</v>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LU0114720955</t>
+          <t>LU0640476718</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Global Health Care A EUR</t>
+          <t>Fidelity Funds - Sustainable Consumer Brands A EUR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2021,7 +2045,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azionari Salute/Pharma</t>
+          <t>Azionari Consumi/Lusso</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2030,13 +2054,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>62.42</v>
-      </c>
-      <c r="H33" t="n">
-        <v>62.1755</v>
-      </c>
-      <c r="I33" t="n">
-        <v>49.61</v>
+        <v>72.25199890136719</v>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
@@ -2045,32 +2063,32 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LU0329630130</t>
+          <t>LU0069450822</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Global Healthcare A EUR</t>
+          <t>Fidelity Funds - America Fund A EUR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azionari Salute/Pharma</t>
+          <t>Azionari USA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2078,6 +2096,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G34" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="H34" t="n">
+        <v>15.9705</v>
+      </c>
+      <c r="I34" t="n">
+        <v>55.08</v>
+      </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2085,7 +2112,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2095,22 +2122,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LU0329455071</t>
+          <t>LU1706106447</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Candriam Equities L Oncology Impact C EUR</t>
+          <t>Nordea 1 - European Sustainable Stars Equity BP EUR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Candriam</t>
+          <t>Nordea</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azionari Salute/Pharma</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2118,6 +2145,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G35" t="n">
+        <v>203.06</v>
+      </c>
+      <c r="H35" t="n">
+        <v>200.7005</v>
+      </c>
+      <c r="I35" t="n">
+        <v>58.56</v>
+      </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2125,22 +2161,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>2</v>
+      <c r="A36" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LU0473185139</t>
+          <t>LU0261959422</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Global Financial Services A EUR</t>
+          <t>Fidelity Funds - European Dynamic Growth Fund A-Acc-EUR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2150,7 +2186,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azionari Finanziari</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2159,13 +2195,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>24.64</v>
+        <v>31.76</v>
       </c>
       <c r="H36" t="n">
-        <v>24.5355</v>
+        <v>31.87</v>
       </c>
       <c r="I36" t="n">
-        <v>57.78</v>
+        <v>45.48</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
@@ -2174,32 +2210,32 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LU0210527791</t>
+          <t>LU0048597586</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Europe Equity A EUR</t>
+          <t>Fidelity Funds - Asia Focus A EUR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azionari Finanziari</t>
+          <t>Azionari Asia Pacifico</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2208,13 +2244,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="H37" t="n">
-        <v>31.8945</v>
-      </c>
-      <c r="I37" t="n">
-        <v>68.88</v>
+        <v>12.50300025939941</v>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
@@ -2223,32 +2253,32 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>2</v>
+      <c r="A38" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LU0363470070</t>
+          <t>LU2401078998</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DWS Invest Global Infrastructure LC</t>
+          <t>Nordea 1 - Global Sustainable Stars Equity Fund AF EUR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Nordea</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azionari Infrastrutture</t>
+          <t>Azionari Globali</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2257,13 +2287,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>158.61</v>
+        <v>243.94</v>
       </c>
       <c r="H38" t="n">
-        <v>154.07</v>
+        <v>240.2335</v>
       </c>
       <c r="I38" t="n">
-        <v>82.47</v>
+        <v>63.5</v>
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
@@ -2272,7 +2302,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2282,22 +2312,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LU0187079347</t>
+          <t>LU1269890163</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Invesco Global Consumer Trends A EUR</t>
+          <t>Candriam Bonds Euro High Yield Class C (Q) EUR Dis</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Candriam</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azionari Consumi/Lusso</t>
+          <t>Obbligazionari High Yield</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2306,13 +2336,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>373.11</v>
+        <v>157.01</v>
       </c>
       <c r="H39" t="n">
-        <v>372.299</v>
+        <v>157.212</v>
       </c>
       <c r="I39" t="n">
-        <v>51.21</v>
+        <v>36.64</v>
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
@@ -2321,32 +2351,32 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LU0640476718</t>
+          <t>FR0010510800</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Sustainable Consumer Brands A EUR</t>
+          <t>Amundi Fds - Euro Government Bond A EUR C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azionari Consumi/Lusso</t>
+          <t>Monetari Euro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2355,7 +2385,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>72.25199890136719</v>
+        <v>113.1480026245117</v>
+      </c>
+      <c r="H40" t="n">
+        <v>113.0768</v>
+      </c>
+      <c r="I40" t="n">
+        <v>70.62</v>
       </c>
       <c r="J40" s="1" t="inlineStr">
         <is>
@@ -2364,22 +2400,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LU0210534433</t>
+          <t>LU0568621618</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - US Growth A EUR</t>
+          <t>JPMorgan Funds - Euro Government Liquidity A EUR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2389,7 +2425,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azionari USA</t>
+          <t>Monetari Euro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2397,6 +2433,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G41" t="n">
+        <v>128.8000030517578</v>
+      </c>
+      <c r="H41" t="n">
+        <v>128.617</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
       <c r="J41" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2404,32 +2449,32 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LU0069450822</t>
+          <t>LU0987184941</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fidelity Funds - America Fund A EUR</t>
+          <t>Amundi Funds - Absolute Return Forex R EUR (C)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azionari USA</t>
+          <t>Fondi Flessibili</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2438,13 +2483,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>16.1</v>
+        <v>103.64</v>
       </c>
       <c r="H42" t="n">
-        <v>15.849</v>
+        <v>103.392</v>
       </c>
       <c r="I42" t="n">
-        <v>64.22</v>
+        <v>76.47</v>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
@@ -2453,7 +2498,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2463,22 +2508,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LU0210073469</t>
+          <t>LU0557854147</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Europe Dynamic A EUR</t>
+          <t>Amundi Funds - Asia Equity Focus A EUR (C)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Azionari Pacifico</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2486,6 +2531,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G43" t="n">
+        <v>226.77</v>
+      </c>
+      <c r="H43" t="n">
+        <v>219.028</v>
+      </c>
+      <c r="I43" t="n">
+        <v>73.76000000000001</v>
+      </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2493,7 +2547,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2557,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LU0346388373</t>
+          <t>LU0568620560</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nordea 1 - European Stars Equity BP EUR</t>
+          <t>Amundi F. Cash EUR A2 EUR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nordea</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Fondi di Mercato Monetario Euro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2527,13 +2581,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>29.99</v>
+        <v>106.12</v>
       </c>
       <c r="H44" t="n">
-        <v>29.49</v>
+        <v>106.096</v>
       </c>
       <c r="I44" t="n">
-        <v>71.55</v>
+        <v>100</v>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
@@ -2542,32 +2596,32 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LU0119750205</t>
+          <t>LU2386146430</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fidelity Funds - European Growth A EUR</t>
+          <t>Amundi Funds - Emerging Markets Equity Select A2 EUR (C)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2576,13 +2630,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>30.93</v>
+        <v>82.33</v>
       </c>
       <c r="H45" t="n">
-        <v>30.362</v>
+        <v>79.8175</v>
       </c>
       <c r="I45" t="n">
-        <v>78.47</v>
+        <v>70.97</v>
       </c>
       <c r="J45" s="1" t="inlineStr">
         <is>
@@ -2591,7 +2645,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2601,22 +2655,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LU0161332480</t>
+          <t>LU0568583420</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Japan Equity A EUR</t>
+          <t>Amundi Funds - Equity Japan Target A EUR (C)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azionari Giappone</t>
+          <t>Azionari Paese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2624,6 +2678,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G46" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="H46" t="n">
+        <v>316.654</v>
+      </c>
+      <c r="I46" t="n">
+        <v>67.95999999999999</v>
+      </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2631,32 +2694,32 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LU0413542167</t>
+          <t>LU0616241476</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Schroders ISF Japanese Equity A EUR Hdg</t>
+          <t>Amundi Funds - Euro Aggregate Bond A EUR (C)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Schroders</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azionari Giappone</t>
+          <t>Obb. Altre Special.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2665,13 +2728,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>59.19</v>
+        <v>134.57</v>
       </c>
       <c r="H47" t="n">
-        <v>56.95</v>
+        <v>133.8405</v>
       </c>
       <c r="I47" t="n">
-        <v>77.90000000000001</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
@@ -2680,7 +2743,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2690,22 +2753,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LU0210526066</t>
+          <t>LU0518421895</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Pacific Equity A EUR</t>
+          <t>Amundi Funds - Euro Government Bond Responsible A EUR (C)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azionari Asia Pacifico</t>
+          <t>Obb. Euro Governativi M/L Termine</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2713,6 +2776,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G48" t="n">
+        <v>125.16</v>
+      </c>
+      <c r="H48" t="n">
+        <v>124.201</v>
+      </c>
+      <c r="I48" t="n">
+        <v>87.31</v>
+      </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2720,32 +2792,32 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LU0048597586</t>
+          <t>LU1883303551</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fidelity Funds - Asia Focus A EUR</t>
+          <t>Amundi Funds - Euroland Equity A CHF Hgd (C)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azionari Asia Pacifico</t>
+          <t>Azionari Area Euro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2754,7 +2826,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>12.48900032043457</v>
+        <v>111.9700012207031</v>
+      </c>
+      <c r="H49" t="n">
+        <v>109.2185</v>
+      </c>
+      <c r="I49" t="n">
+        <v>68.13</v>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
@@ -2763,7 +2841,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2773,22 +2851,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LU0210526579</t>
+          <t>LU0568607203</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - China A EUR</t>
+          <t>Amundi Funds - Euroland Equity Small Cap Select A EUR (C)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azionari Cina</t>
+          <t>Azionari Area Euro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2796,6 +2874,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G50" t="n">
+        <v>258.26</v>
+      </c>
+      <c r="H50" t="n">
+        <v>256.88</v>
+      </c>
+      <c r="I50" t="n">
+        <v>55.18</v>
+      </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2803,32 +2890,32 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LU0333810181</t>
+          <t>LU1883310846</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - India A EUR</t>
+          <t>Amundi Funds - Europe Equity Income Select A2 AUD H QTI D</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azionari India</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2836,6 +2923,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G51" t="n">
+        <v>56.29000091552734</v>
+      </c>
+      <c r="H51" t="n">
+        <v>55.1783</v>
+      </c>
+      <c r="I51" t="n">
+        <v>68.39</v>
+      </c>
       <c r="J51" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2843,7 +2939,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2853,22 +2949,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LU0210534516</t>
+          <t>LU1883306497</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Global Select Equity A EUR</t>
+          <t>Amundi Funds - European Equity Small Cap A EUR (C)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azionari Globali</t>
+          <t>Azionari Europa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2876,6 +2972,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G52" t="n">
+        <v>221.39</v>
+      </c>
+      <c r="H52" t="n">
+        <v>221.319</v>
+      </c>
+      <c r="I52" t="n">
+        <v>51.08</v>
+      </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2883,32 +2988,32 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LU0605515377</t>
+          <t>LU3081003082</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nordea 1 - Global Stars Equity BP EUR</t>
+          <t>Amundi Funds - Absolute Return Global Opportunities Bond A EUR MTD D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nordea</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azionari Globali</t>
+          <t>Obb. Altre Special.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2917,13 +3022,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>36.6</v>
+        <v>50.42</v>
       </c>
       <c r="H53" t="n">
-        <v>35.596</v>
+        <v>50.3505</v>
       </c>
       <c r="I53" t="n">
-        <v>92.69</v>
+        <v>59.83</v>
       </c>
       <c r="J53" s="1" t="inlineStr">
         <is>
@@ -2932,7 +3037,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -2942,22 +3047,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LU0210531934</t>
+          <t>LU2330497517</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Europe High Yield Bond A EUR</t>
+          <t>Amundi Funds - Global Corporate Bond Select A2 EUR Hedged Acc</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Obbligazionari High Yield</t>
+          <t>Obb. Intern. Corporate Investment Grade</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2965,6 +3070,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G54" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="H54" t="n">
+        <v>46.734</v>
+      </c>
+      <c r="I54" t="n">
+        <v>79.70999999999999</v>
+      </c>
       <c r="J54" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2972,32 +3086,32 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LU0159052710</t>
+          <t>LU2531474588</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Candriam Bonds Euro High Yield C EUR</t>
+          <t>Amundi Funds Global Equity Climate A USD Capitalisation</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Candriam</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Obbligazionari High Yield</t>
+          <t>Azionari Internazionali</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3006,7 +3120,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1028.495971679688</v>
+        <v>88.23999786376953</v>
+      </c>
+      <c r="H55" t="n">
+        <v>87.523</v>
+      </c>
+      <c r="I55" t="n">
+        <v>57.17</v>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
@@ -3015,32 +3135,32 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LU0155953517</t>
+          <t>LU1883318666</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fidelity Funds - European High Yield A EUR</t>
+          <t>Amundi Funds - Global Equity Responsible A CHF (C)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Obbligazionari High Yield</t>
+          <t>Azionari Altri Settori</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3048,6 +3168,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G56" t="n">
+        <v>488.1400146484375</v>
+      </c>
+      <c r="H56" t="n">
+        <v>477.475</v>
+      </c>
+      <c r="I56" t="n">
+        <v>62.67</v>
+      </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3055,7 +3184,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3065,22 +3194,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LU0522351971</t>
+          <t>LU1162499526</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Emerging Markets Debt A EUR Hdg</t>
+          <t>Amundi Funds - Global High Yield Bond A EUR Hgd (C)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Obbligazionari Mercati Emergenti</t>
+          <t>Obb. Dollaro High Yield</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3088,6 +3217,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G57" t="n">
+        <v>114.07</v>
+      </c>
+      <c r="H57" t="n">
+        <v>113.925</v>
+      </c>
+      <c r="I57" t="n">
+        <v>58.25</v>
+      </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3095,22 +3233,22 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LU0238205289</t>
+          <t>LU0442405998</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Amundi Fds - Emerging Markets Bond A EUR C</t>
+          <t>Amundi Funds - Global Inflation Short Duration Bond A EUR (C)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3120,7 +3258,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Obbligazionari Mercati Emergenti</t>
+          <t>Obb. Intern. Governativi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3129,13 +3267,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>23.89</v>
+        <v>105.32</v>
       </c>
       <c r="H58" t="n">
-        <v>23.614</v>
+        <v>105.189</v>
       </c>
       <c r="I58" t="n">
-        <v>72.51000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J58" s="1" t="inlineStr">
         <is>
@@ -3144,7 +3282,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3154,22 +3292,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LU0210531850</t>
+          <t>LU1883327907</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Global Bond Opportunities A EUR Hdg</t>
+          <t>Amundi Funds - Global Multi-Asset A USD (C)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Obbligazionari Globali</t>
+          <t>Bilanciati Obbligazionari</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3177,6 +3315,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G59" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>169.8945</v>
+      </c>
+      <c r="I59" t="n">
+        <v>57.58</v>
+      </c>
       <c r="J59" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3184,7 +3331,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3194,22 +3341,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LU0168060498</t>
+          <t>LU1883334275</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nordea 1 - European Covered Bond BP EUR</t>
+          <t>Amundi Funds - Global Subordinated Bond A EUR (C)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nordea</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Obbligazionari Globali</t>
+          <t>Obb. Altre Special.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3217,6 +3364,15 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="G60" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>75.00149999999999</v>
+      </c>
+      <c r="I60" t="n">
+        <v>96.48999999999999</v>
+      </c>
       <c r="J60" s="1" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3224,22 +3380,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FR0010510800</t>
+          <t>LU0945151578</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Amundi Fds - Euro Government Bond A EUR C</t>
+          <t>Amundi Funds - Impact Euro Corporate Short Term Green Bond A EUR (C)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3249,7 +3405,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Monetari Euro</t>
+          <t>Obb. Euro Corporate Investment Grade</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3258,13 +3414,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>113.167</v>
+        <v>106.05</v>
       </c>
       <c r="H61" t="n">
-        <v>113.0675</v>
+        <v>105.9255</v>
       </c>
       <c r="I61" t="n">
-        <v>73.84</v>
+        <v>81.06</v>
       </c>
       <c r="J61" s="1" t="inlineStr">
         <is>
@@ -3273,7 +3429,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3283,22 +3439,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LU0568621618</t>
+          <t>LU2585853059</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JPMorgan Funds - Euro Government Liquidity A EUR</t>
+          <t>Amundi Funds - Income Opportunities A2 AUD H MTD3 (D)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Monetari Euro</t>
+          <t>Fondi Flessibili</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3307,13 +3463,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>128.8</v>
+        <v>56.68999862670898</v>
       </c>
       <c r="H62" t="n">
-        <v>128.617</v>
+        <v>56.2893</v>
       </c>
       <c r="I62" t="n">
-        <v>100</v>
+        <v>64.94</v>
       </c>
       <c r="J62" s="1" t="inlineStr">
         <is>
@@ -3322,22 +3478,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LU0987184941</t>
+          <t>LU1923161894</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Amundi Funds - Absolute Return Forex R EUR (C)</t>
+          <t>Amundi Funds - Japan Equity Select A USD (C)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3347,7 +3503,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fondi Flessibili</t>
+          <t>Azionari Pacifico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3356,22 +3512,22 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>103.65</v>
+        <v>81.03</v>
       </c>
       <c r="H63" t="n">
-        <v>103.347</v>
+        <v>77.80200000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>80.25</v>
-      </c>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+        <v>63.81</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3537,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LU0557854147</t>
+          <t>LU0552029406</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Amundi Funds - Asia Equity Focus A EUR (C)</t>
+          <t>Amundi Funds - Latin America Equity A EUR (C)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3396,7 +3552,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azionari Pacifico</t>
+          <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3405,13 +3561,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>224.89</v>
+        <v>126.36</v>
       </c>
       <c r="H64" t="n">
-        <v>218.2445</v>
+        <v>123.431</v>
       </c>
       <c r="I64" t="n">
-        <v>69.01000000000001</v>
+        <v>62.06</v>
       </c>
       <c r="J64" s="1" t="inlineStr">
         <is>
@@ -3420,22 +3576,22 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LU0568620560</t>
+          <t>LU1883336569</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Amundi F. Cash EUR A2 EUR</t>
+          <t>Amundi Funds - Optimal Yield A EUR (C)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3445,7 +3601,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fondi di Mercato Monetario Euro</t>
+          <t>Obb. Flessibili</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3454,13 +3610,13 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>106.12</v>
+        <v>118.04</v>
       </c>
       <c r="H65" t="n">
-        <v>106.0725</v>
+        <v>117.8</v>
       </c>
       <c r="I65" t="n">
-        <v>100</v>
+        <v>71.58</v>
       </c>
       <c r="J65" s="1" t="inlineStr">
         <is>
@@ -3469,7 +3625,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3635,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LU2386146430</t>
+          <t>LU1883339233</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Amundi Funds - Emerging Markets Equity Select A2 EUR (C)</t>
+          <t>Amundi Funds - Optimal Yield Short Term A EUR (C)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3494,7 +3650,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azionari Paesi Emergenti</t>
+          <t>Obb. Flessibili</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3503,13 +3659,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>81.45</v>
+        <v>58.78</v>
       </c>
       <c r="H66" t="n">
-        <v>79.586</v>
+        <v>58.682</v>
       </c>
       <c r="I66" t="n">
-        <v>65.90000000000001</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="J66" s="1" t="inlineStr">
         <is>
@@ -3518,7 +3674,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3684,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LU0568583420</t>
+          <t>LU1880401101</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amundi Funds - Equity Japan Target A EUR (C)</t>
+          <t>Amundi Funds - US Bond A EUR (C)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3543,7 +3699,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azionari Paese</t>
+          <t>Obb. Dollaro Governativi M/L Termine</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3552,13 +3708,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>329.46</v>
+        <v>53.09</v>
       </c>
       <c r="H67" t="n">
-        <v>316.654</v>
+        <v>52.463</v>
       </c>
       <c r="I67" t="n">
-        <v>67.95999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
@@ -3567,22 +3723,22 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LU0616241476</t>
+          <t>LU2559893917</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Amundi Funds - Euro Aggregate Bond A EUR (C)</t>
+          <t>Amundi Funds - US Corporate Bond Climate A USD (C)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3592,7 +3748,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Obb. Altre Special.</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3601,13 +3757,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>134.38</v>
+        <v>58.06000137329102</v>
       </c>
       <c r="H68" t="n">
-        <v>133.7755</v>
+        <v>57.7105</v>
       </c>
       <c r="I68" t="n">
-        <v>86.95999999999999</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="J68" s="1" t="inlineStr">
         <is>
@@ -3616,7 +3772,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3782,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LU2259111008</t>
+          <t>LU3238210200</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Amundi Funds - Emerging Markets Green Bond G EURO Hedged (C)</t>
+          <t>Amundi Funds - US Corporate Bond Select A EUR Hgd AD (D)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3641,7 +3797,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Obb. Flessibili</t>
+          <t>Obb. Dollaro Corporate Investment Grade</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3650,13 +3806,13 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>4.31</v>
+        <v>50.64</v>
       </c>
       <c r="H69" t="n">
-        <v>4.299</v>
+        <v>50.331</v>
       </c>
       <c r="I69" t="n">
-        <v>100</v>
+        <v>77.36</v>
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
@@ -3665,7 +3821,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3831,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LU0518421895</t>
+          <t>LU1883854199</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Amundi Funds - Euro Government Bond Responsible A EUR (C)</t>
+          <t>Amundi Funds - US Equity Fundamental Growth A EUR C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3690,7 +3846,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Obb. Euro Governativi M/L Termine</t>
+          <t>Azionari America</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3699,13 +3855,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>124.91</v>
+        <v>550.7</v>
       </c>
       <c r="H70" t="n">
-        <v>124.1255</v>
+        <v>567.1135</v>
       </c>
       <c r="I70" t="n">
-        <v>85.56</v>
+        <v>30.23</v>
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
@@ -3714,22 +3870,22 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>2</v>
+      <c r="A71" t="n">
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LU1883303551</t>
+          <t>LU1883859230</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Amundi Funds - Euroland Equity A CHF Hgd (C)</t>
+          <t>Amundi Funds - US Equity Research A EUR (C)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3739,7 +3895,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azionari Area Euro</t>
+          <t>Azionari America</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3748,13 +3904,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>110.38</v>
+        <v>24.16</v>
       </c>
       <c r="H71" t="n">
-        <v>108.996</v>
+        <v>23.984</v>
       </c>
       <c r="I71" t="n">
-        <v>59.5</v>
+        <v>54.93</v>
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
@@ -3763,7 +3919,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3929,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LU0568607203</t>
+          <t>LU2146567529</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Amundi Funds - Euroland Equity Small Cap Select A EUR (C)</t>
+          <t>Amundi Funds - US Equity Select A EUR (C)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3788,7 +3944,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azionari Area Euro</t>
+          <t>Azionari America</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3797,13 +3953,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>260.05</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>256.742</v>
+        <v>81.0485</v>
       </c>
       <c r="I72" t="n">
-        <v>62.11</v>
+        <v>46.8</v>
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
@@ -3812,32 +3968,32 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>2</v>
+      <c r="A73" t="n">
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LU1883310846</t>
+          <t>FR0010149120</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Amundi Funds - Europe Equity Income Select A2 AUD H QTI D</t>
+          <t>Carmignac Sécurité AW Cap EUR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3846,13 +4002,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="H73" t="n">
-        <v>55.0756</v>
-      </c>
-      <c r="I73" t="n">
-        <v>63.37</v>
+        <v>1926.119995117188</v>
       </c>
       <c r="J73" s="1" t="inlineStr">
         <is>
@@ -3861,7 +4011,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3871,22 +4021,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LU1883306497</t>
+          <t>FR0010312660</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Amundi Funds - European Equity Small Cap A EUR (C)</t>
+          <t>Carmignac Investissement E EUR Acc</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azionari Europa</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3895,13 +4045,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>222.76</v>
+        <v>346.35</v>
       </c>
       <c r="H74" t="n">
-        <v>221.3005</v>
+        <v>348.8645</v>
       </c>
       <c r="I74" t="n">
-        <v>56.42</v>
+        <v>31.33</v>
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
@@ -3910,7 +4060,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -3920,22 +4070,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LU3081003082</t>
+          <t>LU0336083810</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Amundi Funds - Absolute Return Global Opportunities Bond A EUR MTD D</t>
+          <t>Carmignac Asia Discovery A EUR Acc EUR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Obb. Altre Special.</t>
+          <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3944,13 +4094,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="H75" t="n">
-        <v>50.344</v>
-      </c>
-      <c r="I75" t="n">
-        <v>63.2</v>
+        <v>2658.722900390625</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
@@ -3959,32 +4103,32 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>3</v>
+      <c r="A76" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LU2330497517</t>
+          <t>FR0011269182</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Amundi Funds - Global Corporate Bond Select A2 EUR Hedged Acc</t>
+          <t>Carmignac Investissement A EUR Ydis</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Obb. Intern. Corporate Investment Grade</t>
+          <t>Azionari Internazionali</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3993,13 +4137,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>46.91</v>
+        <v>280.03</v>
       </c>
       <c r="H76" t="n">
-        <v>46.7155</v>
+        <v>278.533</v>
       </c>
       <c r="I76" t="n">
-        <v>77.02</v>
+        <v>47.96</v>
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
@@ -4008,32 +4152,32 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" t="n">
         <v>2</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LU2531474588</t>
+          <t>LU1623762843</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Amundi Funds Global Equity Climate A USD Capitalisation</t>
+          <t>Carmignac Credit A EUR Acc</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azionari Internazionali</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4042,13 +4186,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>87.56999999999999</v>
+        <v>159.9700012207031</v>
       </c>
       <c r="H77" t="n">
-        <v>87.437</v>
+        <v>159.493</v>
       </c>
       <c r="I77" t="n">
-        <v>52.14</v>
+        <v>77.12</v>
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
@@ -4057,32 +4201,32 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>2</v>
+      <c r="A78" t="n">
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LU1883318666</t>
+          <t>FR0010149302</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Amundi Funds - Global Equity Responsible A CHF (C)</t>
+          <t>Carmignac Emergents A EUR Acc</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azionari Altri Settori</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4091,13 +4235,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>484.28</v>
-      </c>
-      <c r="H78" t="n">
-        <v>476.854</v>
-      </c>
-      <c r="I78" t="n">
-        <v>57.81</v>
+        <v>1638.321044921875</v>
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
@@ -4106,7 +4244,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4116,22 +4254,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LU1162499526</t>
+          <t>FR0011269083</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Amundi Funds - Global High Yield Bond A EUR Hgd (C)</t>
+          <t>Carmignac Sécurité AW EUR Ydis</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Obb. Dollaro High Yield</t>
+          <t>Fondi Flessibili</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4140,13 +4278,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>114.18</v>
-      </c>
-      <c r="H79" t="n">
-        <v>113.9135</v>
-      </c>
-      <c r="I79" t="n">
-        <v>67.89</v>
+        <v>99.56800079345703</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
@@ -4155,7 +4287,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4165,22 +4297,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LU0442405998</t>
+          <t>FR0011269349</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Amundi Funds - Global Inflation Short Duration Bond A EUR (C)</t>
+          <t>Carmignac Emergents A EUR Ydis</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Obb. Intern. Governativi</t>
+          <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4189,13 +4321,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>105.21</v>
-      </c>
-      <c r="H80" t="n">
-        <v>105.168</v>
-      </c>
-      <c r="I80" t="n">
-        <v>58.45</v>
+        <v>212.9100036621094</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -4204,32 +4330,32 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LU1883327907</t>
+          <t>LU1317704051</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Amundi Funds - Global Multi-Asset A USD (C)</t>
+          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bilanciati Obbligazionari</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4238,13 +4364,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>169.65</v>
+        <v>190.82</v>
       </c>
       <c r="H81" t="n">
-        <v>169.7255</v>
+        <v>189.5985</v>
       </c>
       <c r="I81" t="n">
-        <v>54.24</v>
+        <v>62.27</v>
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
@@ -4253,7 +4379,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4263,22 +4389,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LU1883334275</t>
+          <t>LU1163533349</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Amundi Funds - Global Subordinated Bond A EUR (C)</t>
+          <t>Carmignac Patrimoine E EUR Minc</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Obb. Altre Special.</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4287,13 +4413,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>75.23</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>74.9725</v>
+        <v>69.0185</v>
       </c>
       <c r="I82" t="n">
-        <v>95.92</v>
+        <v>35.68</v>
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
@@ -4302,7 +4428,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4312,22 +4438,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LU0945151578</t>
+          <t>FR0011269588</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Amundi Funds - Impact Euro Corporate Short Term Green Bond A EUR (C)</t>
+          <t>Carmignac Patrimoine A EUR Ydis</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Obb. Euro Corporate Investment Grade</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4336,13 +4462,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>105.99</v>
-      </c>
-      <c r="H83" t="n">
-        <v>105.9095</v>
-      </c>
-      <c r="I83" t="n">
-        <v>77.63</v>
+        <v>127.3740005493164</v>
       </c>
       <c r="J83" s="1" t="inlineStr">
         <is>
@@ -4351,32 +4471,32 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>2</v>
+      <c r="A84" t="n">
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LU2585853059</t>
+          <t>LU1163533422</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Amundi Funds - Income Opportunities A2 AUD H MTD3 (D)</t>
+          <t>Carmignac Patrimoine A EUR Minc</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fondi Flessibili</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4385,13 +4505,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>56.51</v>
+        <v>72.61</v>
       </c>
       <c r="H84" t="n">
-        <v>56.2285</v>
+        <v>72.8115</v>
       </c>
       <c r="I84" t="n">
-        <v>61.53</v>
+        <v>36.35</v>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
@@ -4400,32 +4520,32 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>2</v>
+      <c r="A85" t="n">
+        <v>3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LU1923161894</t>
+          <t>FR0010135103</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Amundi Funds - Japan Equity Select A USD (C)</t>
+          <t>Carmignac Patrimoine A EUR Acc</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azionari Pacifico</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4434,13 +4554,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>81.97</v>
-      </c>
-      <c r="H85" t="n">
-        <v>77.434</v>
-      </c>
-      <c r="I85" t="n">
-        <v>69.06</v>
+        <v>798.1339721679688</v>
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
@@ -4449,7 +4563,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4459,22 +4573,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LU0552029406</t>
+          <t>FR0010306142</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Amundi Funds - Latin America Equity A EUR (C)</t>
+          <t>Carmignac Patrimoine E EUR Acc</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azionari Paesi Emergenti</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4483,13 +4597,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>127.65</v>
+        <v>191.32</v>
       </c>
       <c r="H86" t="n">
-        <v>123.0555</v>
+        <v>191.6595</v>
       </c>
       <c r="I86" t="n">
-        <v>67.40000000000001</v>
+        <v>39.1</v>
       </c>
       <c r="J86" s="1" t="inlineStr">
         <is>
@@ -4498,7 +4612,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4508,22 +4622,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LU1883336569</t>
+          <t>LU0336084032</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Amundi Funds - Optimal Yield A EUR (C)</t>
+          <t>Carmignac Flexible Bond A EUR Acc</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Obb. Flessibili</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4532,13 +4646,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>118.01</v>
-      </c>
-      <c r="H87" t="n">
-        <v>117.7825</v>
-      </c>
-      <c r="I87" t="n">
-        <v>70.90000000000001</v>
+        <v>1380.400024414062</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
@@ -4547,7 +4655,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4557,22 +4665,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LU1883339233</t>
+          <t>LU0992631050</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Amundi Funds - Optimal Yield Short Term A EUR (C)</t>
+          <t>Carmignac Flexible Bond A EUR Ydis</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Obb. Flessibili</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4581,13 +4689,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>58.77</v>
-      </c>
-      <c r="H88" t="n">
-        <v>58.6745</v>
-      </c>
-      <c r="I88" t="n">
-        <v>71.04000000000001</v>
+        <v>1090.800048828125</v>
       </c>
       <c r="J88" s="1" t="inlineStr">
         <is>
@@ -4596,7 +4698,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -4606,22 +4708,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LU1880401101</t>
+          <t>LU1299302684</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Amundi Funds - US Bond A EUR (C)</t>
+          <t>Carmignac Flexible Bond A EUR Minc</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Obb. Dollaro Governativi M/L Termine</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4630,13 +4732,13 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>53.01</v>
+        <v>976.27</v>
       </c>
       <c r="H89" t="n">
-        <v>52.411</v>
+        <v>979.1155</v>
       </c>
       <c r="I89" t="n">
-        <v>62.79</v>
+        <v>32.23</v>
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
@@ -4645,27 +4747,27 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" t="n">
         <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LU2559893917</t>
+          <t>LU1317704135</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Amundi Funds - US Corporate Bond Climate A USD (C)</t>
+          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Carmignac</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4679,13 +4781,13 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>58.04</v>
+        <v>178.94</v>
       </c>
       <c r="H90" t="n">
-        <v>57.682</v>
+        <v>177.819</v>
       </c>
       <c r="I90" t="n">
-        <v>71.66</v>
+        <v>61.96</v>
       </c>
       <c r="J90" s="1" t="inlineStr">
         <is>
@@ -4694,1071 +4796,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>3</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>LU3238210200</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Amundi Funds - US Corporate Bond Select A EUR Hgd AD (D)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Amundi</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Obb. Dollaro Corporate Investment Grade</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>50.59</v>
-      </c>
-      <c r="H91" t="n">
-        <v>50.309</v>
-      </c>
-      <c r="I91" t="n">
-        <v>75.39</v>
-      </c>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>3</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>LU1883854199</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Amundi Funds - US Equity Fundamental Growth A EUR C</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Amundi</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Azionari America</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>559.1900000000001</v>
-      </c>
-      <c r="H92" t="n">
-        <v>569.5715</v>
-      </c>
-      <c r="I92" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>3</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>LU1883859230</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Amundi Funds - US Equity Research A EUR (C)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Amundi</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Azionari America</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="H93" t="n">
-        <v>23.9735</v>
-      </c>
-      <c r="I93" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="J93" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>3</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>LU2146567529</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Amundi Funds - US Equity Select A EUR (C)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Amundi</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Azionari America</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>81.67</v>
-      </c>
-      <c r="H94" t="n">
-        <v>81.0565</v>
-      </c>
-      <c r="I94" t="n">
-        <v>55.32</v>
-      </c>
-      <c r="J94" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>3</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>FR0010149120</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Carmignac Sécurité AW Cap EUR</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>1926.489013671875</v>
-      </c>
-      <c r="J95" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>3</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>FR0010312660</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Carmignac Investissement E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>350.27</v>
-      </c>
-      <c r="H96" t="n">
-        <v>352.5435</v>
-      </c>
-      <c r="I96" t="n">
-        <v>37.09</v>
-      </c>
-      <c r="J96" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>LU0336083810</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Carmignac Asia Discovery A EUR Acc EUR</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Azionari Paesi Emergenti</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>2631.5830078125</v>
-      </c>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>3</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>FR0011269182</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Carmignac Investissement A EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Azionari Internazionali</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>278.88</v>
-      </c>
-      <c r="H98" t="n">
-        <v>280.6295</v>
-      </c>
-      <c r="I98" t="n">
-        <v>43.88</v>
-      </c>
-      <c r="J98" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>2</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>LU1623762843</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Carmignac Credit A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>159.88</v>
-      </c>
-      <c r="H99" t="n">
-        <v>159.425</v>
-      </c>
-      <c r="I99" t="n">
-        <v>75.95999999999999</v>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>FR0010148981</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Carmignac Investissement A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>3</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>FR0010149302</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Carmignac Emergents A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>1634.505981445312</v>
-      </c>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>3</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>FR0011269083</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Carmignac Sécurité AW EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Fondi Flessibili</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>99.53800201416016</v>
-      </c>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>3</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>FR0011269349</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Carmignac Emergents A EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Azionari Paesi Emergenti</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>213.8150024414062</v>
-      </c>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>LU1317704051</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>189.48</v>
-      </c>
-      <c r="H104" t="n">
-        <v>189.364</v>
-      </c>
-      <c r="I104" t="n">
-        <v>52.55</v>
-      </c>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>3</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>LU1163533349</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine E EUR Minc</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
-        <v>69.12</v>
-      </c>
-      <c r="H105" t="n">
-        <v>69.387</v>
-      </c>
-      <c r="I105" t="n">
-        <v>39.82</v>
-      </c>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>3</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>FR0011269588</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine A EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Bilanciati</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>127.7509994506836</v>
-      </c>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>3</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>LU1163533422</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine A EUR Minc</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>72.92</v>
-      </c>
-      <c r="H107" t="n">
-        <v>73.166</v>
-      </c>
-      <c r="I107" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>3</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>FR0010135103</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Bilanciati</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>797.6500244140625</v>
-      </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>3</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>FR0010306142</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Bilanciati</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>192.16</v>
-      </c>
-      <c r="H109" t="n">
-        <v>192.2905</v>
-      </c>
-      <c r="I109" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>3</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>LU0336084032</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>1380.401977539062</v>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>3</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>LU0992631050</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
-        <v>1090.800048828125</v>
-      </c>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>LU1299302684</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Minc</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>977.95</v>
-      </c>
-      <c r="H112" t="n">
-        <v>981.1615</v>
-      </c>
-      <c r="I112" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>LU1317704135</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>177.7</v>
-      </c>
-      <c r="H113" t="n">
-        <v>177.617</v>
-      </c>
-      <c r="I113" t="n">
-        <v>52.26</v>
-      </c>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>2026-02-22 11:56</t>
+          <t>2026-02-24 15:05</t>
         </is>
       </c>
     </row>
@@ -5773,7 +4811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5787,736 +4825,293 @@
           <t>nome</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>motivo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LU1213835603</t>
+          <t>LU2259111008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amundi Fds - Pioneer US Equity Fundamental Growth A EUR C</t>
+          <t>Amundi Funds - Emerging Markets Green Bond G EURO Hedged (C)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LU1213836676</t>
+          <t>LU0172157363</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amundi Fds - China Equity A EUR C</t>
+          <t>BGF World Mining Euro E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LU1882436906</t>
+          <t>LU0171304552</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amundi F. Abs. Return Multi-Strat. E2 EUR</t>
+          <t>BGF World Energy Euro E</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LU1882437110</t>
+          <t>LU0329455071</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amundi F. Abs. Return Multi-Strat. F EUR</t>
+          <t>Candriam Equities L Oncology Impact C EUR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LU1882437201</t>
+          <t>LU0210534433</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amundi F. Abs. Return Multi-Strat. G EUR</t>
+          <t>JPMorgan Funds - US Growth A EUR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LU1882464007</t>
+          <t>LU0210073469</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amundi F. EM Blended Bond G Dis EUR</t>
+          <t>JPMorgan Funds - Europe Dynamic A EUR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LU1882463967</t>
+          <t>LU0161332480</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amundi F. EM Blended Bond G EUR</t>
+          <t>JPMorgan Funds - Japan Equity A EUR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LU1882460351</t>
+          <t>LU0210526066</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amundi F. EM Corp. High Yield Bond E2 Dis EUR</t>
+          <t>JPMorgan Funds - Pacific Equity A EUR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LU1882460278</t>
+          <t>LU0210526579</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amundi F. EM Corp. High Yield Bond E2 EUR</t>
+          <t>JPMorgan Funds - China A EUR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LU1882460518</t>
+          <t>LU0333810181</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amundi F. EM Corp. High Yield Bond F Dis EUR</t>
+          <t>JPMorgan Funds - India A EUR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LU1882461086</t>
+          <t>LU0210534516</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amundi F. EM Corporate Bond G Dis EUR Hdg</t>
+          <t>JPMorgan Funds - Global Select Equity A EUR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LU1882460948</t>
+          <t>LU0210531934</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amundi F. EM Corporate Bond G EUR Hdg</t>
+          <t>JPMorgan Funds - Europe High Yield Bond A EUR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LU1882464775</t>
+          <t>LU0155953517</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amundi F. EM Hard Currency Bond G EUR</t>
+          <t>Fidelity Funds - European High Yield A EUR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LU1882459502</t>
+          <t>LU0522351971</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amundi F. Emerging World Equity E2 EUR</t>
+          <t>JPMorgan Funds - Emerging Markets Debt A EUR Hdg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LU1882459684</t>
+          <t>LU0210531850</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amundi F. Emerging World Equity F EUR</t>
+          <t>JPMorgan Funds - Global Bond Opportunities A EUR Hdg</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LU1882459767</t>
+          <t>LU0168060498</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amundi F. Emerging World Equity G EUR</t>
+          <t>Nordea 1 - European Covered Bond BP EUR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LU1882454297</t>
+          <t>FR0010148981</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amundi F. Euro Corporate Bond Select E2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LU1882454115</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Amundi F. Euro Corporate Bond Select E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LU1882454370</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Amundi F. Euro Corporate Bond Select F EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LU1882454453</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Amundi F. Euro Corporate Bond Select G EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LU1882461087</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Amundi F. Euro Multi-Asset T. Income E2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LU1882461160</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Amundi F. Euro Multi-Asset T. Income G2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LU1882453489</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Amundi F. Europe Equity Climate E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LU1882453562</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Amundi F. Europe Equity Climate F EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LU1882453646</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Amundi F. Europe Equity Climate G EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LU1882454024</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Amundi F. Europe Equity Income Select E2 DisS EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LU1882454107</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Amundi F. Europe Equity Income Select G2 DisS EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LU1882453729</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Amundi F. European Equity Value E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LU1882453992</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Amundi F. European Equity Value F EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LU1882454073</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Amundi F. European Equity Value G EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LU1882456821</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Amundi F. Gl. Aggregate Bond E2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LU1882456748</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Amundi F. Gl. Aggregate Bond E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LU1882457043</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Amundi F. Gl. Aggregate Bond G DisM EUR Hdg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LU1882456904</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Amundi F. Gl. Aggregate Bond G EUR hdg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LU1882457126</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Amundi F. Gl. Corporate Bond G Dis EUR Hdg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LU1882461400</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Amundi F. Gl. Multi-Asset Target Inc. E2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LU1882461590</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Amundi F. Gl. Multi-Asset Target Inc. E2 DisQ EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LU1882454610</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LU1882454883</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity F EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>LU1882455047</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity G EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LU1882455120</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity G EUR Hdg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LU1882455500</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity Income Select E2 DisQ EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LU1882455690</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity Income Select E2 DisS EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LU1882455427</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity Income Select E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>LU1882455773</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Amundi F. Global Equity Income Select G2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LU1882459338</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Amundi F. Japan Equity Value G2 EUR Hdg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LU1882460602</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Amundi F. Pioneer Flexible Opport. E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LU1882460784</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Amundi F. Pioneer Flexible Opport. F EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LU1882460867</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Amundi F. Pioneer Flexible Opport. G EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LU1882460941</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Amundi F. Pioneer Global HY Bond E2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LU1882461089</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Amundi F. Pioneer Global HY Bond E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>LU1882461162</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Amundi F. Pioneer Global HY Bond F Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>LU1882461246</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Amundi F. Pioneer Global HY Bond F EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>LU1882461329</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond E2 Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>LU1882461412</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond E2 DisQ EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>LU1882461594</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond E2 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LU1882461677</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond F Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>LU1882461750</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond F DisQ EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>LU1882461834</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond F EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>LU1882461917</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond G Dis EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>LU1882462056</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Amundi F. Strategic Bond G DisQ EUR</t>
+          <t>Carmignac Investissement A EUR Acc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -538,7 +538,7 @@
         <v>291.67</v>
       </c>
       <c r="H2" t="n">
-        <v>286.101</v>
+        <v>288.1415</v>
       </c>
       <c r="I2" t="n">
         <v>61.92</v>
@@ -550,7 +550,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>369.06</v>
       </c>
       <c r="H3" t="n">
-        <v>346.281</v>
+        <v>352.627</v>
       </c>
       <c r="I3" t="n">
         <v>63.63</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
         <v>315.41</v>
       </c>
       <c r="H4" t="n">
-        <v>295.988</v>
+        <v>301.397</v>
       </c>
       <c r="I4" t="n">
         <v>65.02</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
         <v>18.95</v>
       </c>
       <c r="H5" t="n">
-        <v>18.301</v>
+        <v>18.4835</v>
       </c>
       <c r="I5" t="n">
         <v>65.36</v>
@@ -697,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
         <v>19.99</v>
       </c>
       <c r="H6" t="n">
-        <v>20.076</v>
+        <v>20.0685</v>
       </c>
       <c r="I6" t="n">
         <v>42.22</v>
@@ -746,7 +746,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -832,19 +832,19 @@
         <v>125.74</v>
       </c>
       <c r="H8" t="n">
-        <v>125.5842</v>
+        <v>125.6295</v>
       </c>
       <c r="I8" t="n">
         <v>79.52</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -881,19 +881,19 @@
         <v>94.98</v>
       </c>
       <c r="H9" t="n">
-        <v>94.85299999999999</v>
+        <v>94.8905</v>
       </c>
       <c r="I9" t="n">
         <v>82.16</v>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         <v>17.13</v>
       </c>
       <c r="H10" t="n">
-        <v>17.1214</v>
+        <v>17.1255</v>
       </c>
       <c r="I10" t="n">
         <v>69.59999999999999</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -979,19 +979,19 @@
         <v>7.68</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6715</v>
+        <v>7.6745</v>
       </c>
       <c r="I11" t="n">
         <v>68.19</v>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
         <v>10.83</v>
       </c>
       <c r="H12" t="n">
-        <v>10.8215</v>
+        <v>10.825</v>
       </c>
       <c r="I12" t="n">
         <v>74.66</v>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         <v>123.08</v>
       </c>
       <c r="H13" t="n">
-        <v>122.852</v>
+        <v>122.9215</v>
       </c>
       <c r="I13" t="n">
         <v>62.65</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>149.61</v>
       </c>
       <c r="H14" t="n">
-        <v>149.526</v>
+        <v>149.544</v>
       </c>
       <c r="I14" t="n">
         <v>54.78</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>56.76</v>
       </c>
       <c r="H15" t="n">
-        <v>57.501</v>
+        <v>57.3735</v>
       </c>
       <c r="I15" t="n">
         <v>37.35</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         <v>22.51</v>
       </c>
       <c r="H16" t="n">
-        <v>22.271</v>
+        <v>22.367</v>
       </c>
       <c r="I16" t="n">
         <v>52.57</v>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
         <v>71.75</v>
       </c>
       <c r="H18" t="n">
-        <v>72.699</v>
+        <v>72.5335</v>
       </c>
       <c r="I18" t="n">
         <v>37.19</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>15.17</v>
       </c>
       <c r="H19" t="n">
-        <v>14.9555</v>
+        <v>15.031</v>
       </c>
       <c r="I19" t="n">
         <v>63.25</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         <v>20.1</v>
       </c>
       <c r="H20" t="n">
-        <v>19.7345</v>
+        <v>19.8125</v>
       </c>
       <c r="I20" t="n">
         <v>67.68000000000001</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1469,19 +1469,19 @@
         <v>116.14</v>
       </c>
       <c r="H21" t="n">
-        <v>113.71</v>
+        <v>114.377</v>
       </c>
       <c r="I21" t="n">
         <v>67.59</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
         <v>32.65</v>
       </c>
       <c r="H23" t="n">
-        <v>32.5763</v>
+        <v>32.583</v>
       </c>
       <c r="I23" t="n">
         <v>56.51</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1665,19 +1665,19 @@
         <v>1382.77</v>
       </c>
       <c r="H25" t="n">
-        <v>1334.846</v>
+        <v>1345.8625</v>
       </c>
       <c r="I25" t="n">
         <v>68.48</v>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
         <v>19.18</v>
       </c>
       <c r="H27" t="n">
-        <v>18.847</v>
+        <v>18.942</v>
       </c>
       <c r="I27" t="n">
         <v>66</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
         <v>21.94</v>
       </c>
       <c r="H28" t="n">
-        <v>21.5235</v>
+        <v>21.6945</v>
       </c>
       <c r="I28" t="n">
         <v>68.38</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         <v>62.45</v>
       </c>
       <c r="H29" t="n">
-        <v>62.1505</v>
+        <v>62.2185</v>
       </c>
       <c r="I29" t="n">
         <v>50.07</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
         <v>15.96</v>
       </c>
       <c r="H34" t="n">
-        <v>15.9705</v>
+        <v>15.983</v>
       </c>
       <c r="I34" t="n">
         <v>55.08</v>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>12.50300025939941</v>
+        <v>12.50399971008301</v>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>113.1480026245117</v>
+        <v>113.1679992675781</v>
       </c>
       <c r="H40" t="n">
         <v>113.0768</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2584,19 +2584,19 @@
         <v>106.12</v>
       </c>
       <c r="H44" t="n">
-        <v>106.096</v>
+        <v>106.106</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>81.03</v>
+        <v>81.02999877929688</v>
       </c>
       <c r="H63" t="n">
         <v>77.80200000000001</v>
@@ -3520,14 +3520,14 @@
       <c r="I63" t="n">
         <v>63.81</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
         <v>346.35</v>
       </c>
       <c r="H74" t="n">
-        <v>348.8645</v>
+        <v>347.948</v>
       </c>
       <c r="I74" t="n">
         <v>31.33</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2658.722900390625</v>
+        <v>2658.577880859375</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
         <v>280.03</v>
       </c>
       <c r="H76" t="n">
-        <v>278.533</v>
+        <v>278.456</v>
       </c>
       <c r="I76" t="n">
         <v>47.96</v>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>212.9100036621094</v>
+        <v>213.4109954833984</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="4" t="n">
         <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4367,7 +4367,7 @@
         <v>190.82</v>
       </c>
       <c r="H81" t="n">
-        <v>189.5985</v>
+        <v>189.8105</v>
       </c>
       <c r="I81" t="n">
         <v>62.27</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>68.81999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>69.0185</v>
+        <v>68.9495</v>
       </c>
       <c r="I82" t="n">
         <v>35.68</v>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
         <v>72.61</v>
       </c>
       <c r="H84" t="n">
-        <v>72.8115</v>
+        <v>72.7415</v>
       </c>
       <c r="I84" t="n">
         <v>36.35</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
         <v>191.32</v>
       </c>
       <c r="H86" t="n">
-        <v>191.6595</v>
+        <v>191.6035</v>
       </c>
       <c r="I86" t="n">
         <v>39.1</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
         <v>976.27</v>
       </c>
       <c r="H89" t="n">
-        <v>979.1155</v>
+        <v>978.0105</v>
       </c>
       <c r="I89" t="n">
         <v>32.23</v>
@@ -4747,12 +4747,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" s="4" t="n">
         <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -4784,7 +4784,7 @@
         <v>178.94</v>
       </c>
       <c r="H90" t="n">
-        <v>177.819</v>
+        <v>178.009</v>
       </c>
       <c r="I90" t="n">
         <v>61.96</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-02-24 15:05</t>
+          <t>2026-02-24 16:02</t>
         </is>
       </c>
     </row>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>291.67</v>
+        <v>296.91</v>
       </c>
       <c r="H2" t="n">
-        <v>288.1415</v>
+        <v>289.2315</v>
       </c>
       <c r="I2" t="n">
-        <v>61.92</v>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+        <v>71.08</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>369.06</v>
+        <v>380.52</v>
       </c>
       <c r="H3" t="n">
-        <v>352.627</v>
+        <v>355.4335</v>
       </c>
       <c r="I3" t="n">
-        <v>63.63</v>
+        <v>69.92</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>315.41</v>
+        <v>325.2</v>
       </c>
       <c r="H4" t="n">
-        <v>301.397</v>
+        <v>303.791</v>
       </c>
       <c r="I4" t="n">
-        <v>65.02</v>
+        <v>70.58</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18.95</v>
+        <v>19.23</v>
       </c>
       <c r="H5" t="n">
-        <v>18.4835</v>
+        <v>18.563</v>
       </c>
       <c r="I5" t="n">
-        <v>65.36</v>
+        <v>70.08</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>19.99</v>
+        <v>20.04</v>
       </c>
       <c r="H6" t="n">
-        <v>20.0685</v>
+        <v>20.0695</v>
       </c>
       <c r="I6" t="n">
-        <v>42.22</v>
+        <v>49.53</v>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>51.1</v>
+        <v>51.08</v>
       </c>
       <c r="H7" t="n">
         <v>51.951</v>
@@ -795,7 +795,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>125.74</v>
+        <v>125.72</v>
       </c>
       <c r="H8" t="n">
-        <v>125.6295</v>
+        <v>125.6435</v>
       </c>
       <c r="I8" t="n">
-        <v>79.52</v>
+        <v>74.39</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>94.98</v>
+        <v>94.97</v>
       </c>
       <c r="H9" t="n">
-        <v>94.8905</v>
+        <v>94.9025</v>
       </c>
       <c r="I9" t="n">
-        <v>82.16</v>
+        <v>78.56</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>17.13</v>
+        <v>17.14</v>
       </c>
       <c r="H10" t="n">
-        <v>17.1255</v>
+        <v>17.1275</v>
       </c>
       <c r="I10" t="n">
-        <v>69.59999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
         <v>7.68</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6745</v>
+        <v>7.6755</v>
       </c>
       <c r="I11" t="n">
         <v>68.19</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
         <v>10.83</v>
       </c>
       <c r="H12" t="n">
-        <v>10.825</v>
+        <v>10.826</v>
       </c>
       <c r="I12" t="n">
         <v>74.66</v>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>123.08</v>
+        <v>123.11</v>
       </c>
       <c r="H13" t="n">
-        <v>122.9215</v>
+        <v>122.947</v>
       </c>
       <c r="I13" t="n">
-        <v>62.65</v>
+        <v>64.3</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>149.61</v>
+        <v>149.73</v>
       </c>
       <c r="H14" t="n">
-        <v>149.544</v>
+        <v>149.561</v>
       </c>
       <c r="I14" t="n">
-        <v>54.78</v>
+        <v>62.47</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>56.76</v>
+        <v>58.06</v>
       </c>
       <c r="H15" t="n">
-        <v>57.3735</v>
+        <v>57.393</v>
       </c>
       <c r="I15" t="n">
-        <v>37.35</v>
+        <v>55.14</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>22.51</v>
+        <v>22.53</v>
       </c>
       <c r="H16" t="n">
-        <v>22.367</v>
+        <v>22.387</v>
       </c>
       <c r="I16" t="n">
-        <v>52.57</v>
+        <v>52.97</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18.27</v>
+        <v>18.78</v>
       </c>
       <c r="H17" t="n">
         <v>18.1005</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>71.75</v>
+        <v>73.39</v>
       </c>
       <c r="H18" t="n">
-        <v>72.5335</v>
+        <v>72.5565</v>
       </c>
       <c r="I18" t="n">
-        <v>37.19</v>
+        <v>55</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>15.17</v>
+        <v>15.57</v>
       </c>
       <c r="H19" t="n">
-        <v>15.031</v>
+        <v>15.0735</v>
       </c>
       <c r="I19" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>20.1</v>
+        <v>20.19</v>
       </c>
       <c r="H20" t="n">
-        <v>19.8125</v>
+        <v>19.8565</v>
       </c>
       <c r="I20" t="n">
-        <v>67.68000000000001</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>116.14</v>
+        <v>115.37</v>
       </c>
       <c r="H21" t="n">
-        <v>114.377</v>
+        <v>114.5695</v>
       </c>
       <c r="I21" t="n">
-        <v>67.59</v>
+        <v>61.47</v>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8.220000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="H22" t="n">
         <v>7.9335</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>32.65</v>
+        <v>32.71</v>
       </c>
       <c r="H23" t="n">
-        <v>32.583</v>
+        <v>32.5935</v>
       </c>
       <c r="I23" t="n">
-        <v>56.51</v>
+        <v>57.83</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>7.65</v>
+        <v>7.57</v>
       </c>
       <c r="H24" t="n">
         <v>7.2805</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1382.77</v>
+        <v>1410.59</v>
       </c>
       <c r="H25" t="n">
-        <v>1345.8625</v>
+        <v>1350.6905</v>
       </c>
       <c r="I25" t="n">
-        <v>68.48</v>
+        <v>73.91</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>101.12</v>
+        <v>101.24</v>
       </c>
       <c r="H26" t="n">
         <v>33.9061</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>19.18</v>
+        <v>19.32</v>
       </c>
       <c r="H27" t="n">
-        <v>18.942</v>
+        <v>18.9775</v>
       </c>
       <c r="I27" t="n">
-        <v>66</v>
+        <v>70.31</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1809,22 +1809,22 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>21.94</v>
+        <v>22.65</v>
       </c>
       <c r="H28" t="n">
-        <v>21.6945</v>
+        <v>21.7815</v>
       </c>
       <c r="I28" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+        <v>81.16</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>62.45</v>
+        <v>62.66</v>
       </c>
       <c r="H29" t="n">
-        <v>62.2185</v>
+        <v>62.26</v>
       </c>
       <c r="I29" t="n">
-        <v>50.07</v>
+        <v>55.28</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>282.1</v>
+        <v>283.65</v>
       </c>
       <c r="H30" t="n">
         <v>281.0385</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>25.03</v>
+        <v>25.14</v>
       </c>
       <c r="H31" t="n">
         <v>25.655</v>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>32.43000030517578</v>
+        <v>32.61999893188477</v>
       </c>
       <c r="H32" t="n">
         <v>31.8945</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>72.25199890136719</v>
+        <v>72.44599914550781</v>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>15.96</v>
+        <v>16.07</v>
       </c>
       <c r="H34" t="n">
-        <v>15.983</v>
+        <v>15.9835</v>
       </c>
       <c r="I34" t="n">
-        <v>55.08</v>
+        <v>62.64</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>203.06</v>
+        <v>204.84</v>
       </c>
       <c r="H35" t="n">
         <v>200.7005</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>31.76</v>
+        <v>32.25</v>
       </c>
       <c r="H36" t="n">
         <v>31.87</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>12.50399971008301</v>
+        <v>12.55599975585938</v>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>243.94</v>
+        <v>246.09</v>
       </c>
       <c r="H38" t="n">
         <v>240.2335</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>157.01</v>
+        <v>157.03</v>
       </c>
       <c r="H39" t="n">
         <v>157.212</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>113.1679992675781</v>
+        <v>113.161003112793</v>
       </c>
       <c r="H40" t="n">
         <v>113.0768</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>128.8000030517578</v>
+        <v>128.8600006103516</v>
       </c>
       <c r="H41" t="n">
         <v>128.617</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>103.64</v>
+        <v>103.65</v>
       </c>
       <c r="H42" t="n">
         <v>103.392</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>226.77</v>
+        <v>232.15</v>
       </c>
       <c r="H43" t="n">
         <v>219.028</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2581,22 +2581,22 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>106.12</v>
+        <v>106.15</v>
       </c>
       <c r="H44" t="n">
-        <v>106.106</v>
+        <v>106.1105</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>82.33</v>
+        <v>84.08</v>
       </c>
       <c r="H45" t="n">
         <v>79.8175</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>329.46</v>
+        <v>329.51</v>
       </c>
       <c r="H46" t="n">
         <v>316.654</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>134.57</v>
+        <v>134.6</v>
       </c>
       <c r="H47" t="n">
         <v>133.8405</v>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>111.9700012207031</v>
+        <v>111.4599990844727</v>
       </c>
       <c r="H49" t="n">
         <v>109.2185</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>258.26</v>
+        <v>260.57</v>
       </c>
       <c r="H50" t="n">
         <v>256.88</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>56.29000091552734</v>
+        <v>56.06000137329102</v>
       </c>
       <c r="H51" t="n">
         <v>55.1783</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>221.39</v>
+        <v>222.52</v>
       </c>
       <c r="H52" t="n">
         <v>221.319</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>50.42</v>
+        <v>50.47</v>
       </c>
       <c r="H53" t="n">
         <v>50.3505</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>46.97</v>
+        <v>46.93</v>
       </c>
       <c r="H54" t="n">
         <v>46.734</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>88.23999786376953</v>
+        <v>87.55000305175781</v>
       </c>
       <c r="H55" t="n">
         <v>87.523</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>488.1400146484375</v>
+        <v>484.4700012207031</v>
       </c>
       <c r="H56" t="n">
         <v>477.475</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>114.07</v>
+        <v>114.15</v>
       </c>
       <c r="H57" t="n">
         <v>113.925</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>105.32</v>
+        <v>105.21</v>
       </c>
       <c r="H58" t="n">
         <v>105.189</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>170.5</v>
+        <v>170.6600036621094</v>
       </c>
       <c r="H59" t="n">
         <v>169.8945</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>75.29000000000001</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="H60" t="n">
         <v>75.00149999999999</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>106.05</v>
+        <v>105.99</v>
       </c>
       <c r="H61" t="n">
         <v>105.9255</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>56.68999862670898</v>
+        <v>56.40999984741211</v>
       </c>
       <c r="H62" t="n">
         <v>56.2893</v>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>81.02999877929688</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="H63" t="n">
         <v>77.80200000000001</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>126.36</v>
+        <v>128.36</v>
       </c>
       <c r="H64" t="n">
         <v>123.431</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>118.04</v>
+        <v>118.01</v>
       </c>
       <c r="H65" t="n">
         <v>117.8</v>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>53.09</v>
+        <v>53.03</v>
       </c>
       <c r="H67" t="n">
         <v>52.463</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>58.06000137329102</v>
+        <v>58.06999969482422</v>
       </c>
       <c r="H68" t="n">
         <v>57.7105</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>50.64</v>
+        <v>50.6</v>
       </c>
       <c r="H69" t="n">
         <v>50.331</v>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>550.7</v>
+        <v>562.75</v>
       </c>
       <c r="H70" t="n">
         <v>567.1135</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>24.16</v>
+        <v>24.59</v>
       </c>
       <c r="H71" t="n">
         <v>23.984</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>80.56999999999999</v>
+        <v>81.53</v>
       </c>
       <c r="H72" t="n">
         <v>81.0485</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1926.119995117188</v>
+        <v>1926.787963867188</v>
       </c>
       <c r="J73" s="1" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>346.35</v>
+        <v>355.64</v>
       </c>
       <c r="H74" t="n">
-        <v>347.948</v>
+        <v>348.33</v>
       </c>
       <c r="I74" t="n">
-        <v>31.33</v>
+        <v>61.47</v>
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2658.577880859375</v>
+        <v>2717.27099609375</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4137,13 +4137,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>280.03</v>
+        <v>279.91</v>
       </c>
       <c r="H76" t="n">
-        <v>278.456</v>
+        <v>278.601</v>
       </c>
       <c r="I76" t="n">
-        <v>47.96</v>
+        <v>47.36</v>
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
@@ -4152,22 +4152,22 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LU1623762843</t>
+          <t>FR0010149302</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carmignac Credit A EUR Acc</t>
+          <t>Carmignac Emergents A EUR Acc</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4186,13 +4186,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>159.9700012207031</v>
-      </c>
-      <c r="H77" t="n">
-        <v>159.493</v>
-      </c>
-      <c r="I77" t="n">
-        <v>77.12</v>
+        <v>1650.0419921875</v>
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
@@ -4201,7 +4195,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4205,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FR0010149302</t>
+          <t>FR0011269083</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Carmignac Emergents A EUR Acc</t>
+          <t>Carmignac Sécurité AW EUR Ydis</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4226,7 +4220,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Fondi Flessibili</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4235,7 +4229,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1638.321044921875</v>
+        <v>99.56800079345703</v>
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
@@ -4244,7 +4238,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4248,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FR0011269083</t>
+          <t>FR0011269349</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Carmignac Sécurité AW EUR Ydis</t>
+          <t>Carmignac Emergents A EUR Ydis</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4269,7 +4263,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fondi Flessibili</t>
+          <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4278,7 +4272,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>99.56800079345703</v>
+        <v>215.6589965820312</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
@@ -4287,22 +4281,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>3</v>
+      <c r="A80" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FR0011269349</t>
+          <t>LU1317704051</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Carmignac Emergents A EUR Ydis</t>
+          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4312,7 +4306,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azionari Paesi Emergenti</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4321,7 +4315,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>213.4109954833984</v>
+        <v>190.63</v>
+      </c>
+      <c r="H80" t="n">
+        <v>189.8945</v>
+      </c>
+      <c r="I80" t="n">
+        <v>59.29</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -4330,22 +4330,22 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
-        <v>2</v>
+      <c r="A81" t="n">
+        <v>3</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LU1317704051</t>
+          <t>LU1163533349</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
+          <t>Carmignac Patrimoine E EUR Minc</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4364,13 +4364,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>190.82</v>
+        <v>69.37</v>
       </c>
       <c r="H81" t="n">
-        <v>189.8105</v>
+        <v>68.967</v>
       </c>
       <c r="I81" t="n">
-        <v>62.27</v>
+        <v>54.11</v>
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4389,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LU1163533349</t>
+          <t>FR0011269588</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine E EUR Minc</t>
+          <t>Carmignac Patrimoine A EUR Ydis</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4413,13 +4413,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>68.81999999999999</v>
-      </c>
-      <c r="H82" t="n">
-        <v>68.9495</v>
-      </c>
-      <c r="I82" t="n">
-        <v>35.68</v>
+        <v>128.2530059814453</v>
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
@@ -4428,7 +4422,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4438,12 +4432,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FR0011269588</t>
+          <t>LU1163533422</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Ydis</t>
+          <t>Carmignac Patrimoine A EUR Minc</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4453,7 +4447,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bilanciati</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4462,7 +4456,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>127.3740005493164</v>
+        <v>73.19</v>
+      </c>
+      <c r="H83" t="n">
+        <v>72.76049999999999</v>
+      </c>
+      <c r="I83" t="n">
+        <v>54.86</v>
       </c>
       <c r="J83" s="1" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LU1163533422</t>
+          <t>FR0010135103</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Minc</t>
+          <t>Carmignac Patrimoine A EUR Acc</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4505,13 +4505,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="H84" t="n">
-        <v>72.7415</v>
-      </c>
-      <c r="I84" t="n">
-        <v>36.35</v>
+        <v>800.5250244140625</v>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
@@ -4520,7 +4514,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4524,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FR0010135103</t>
+          <t>FR0010306142</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Acc</t>
+          <t>Carmignac Patrimoine E EUR Acc</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4554,7 +4548,13 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>798.1339721679688</v>
+        <v>192.75</v>
+      </c>
+      <c r="H85" t="n">
+        <v>191.6865</v>
+      </c>
+      <c r="I85" t="n">
+        <v>57.09</v>
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4573,12 +4573,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FR0010306142</t>
+          <t>LU0336084032</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine E EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Acc</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bilanciati</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4597,13 +4597,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>191.32</v>
-      </c>
-      <c r="H86" t="n">
-        <v>191.6035</v>
-      </c>
-      <c r="I86" t="n">
-        <v>39.1</v>
+        <v>1380.400024414062</v>
       </c>
       <c r="J86" s="1" t="inlineStr">
         <is>
@@ -4612,7 +4606,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4616,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LU0336084032</t>
+          <t>LU0992631050</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Carmignac Flexible Bond A EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Ydis</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4646,7 +4640,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1380.400024414062</v>
+        <v>1090.800048828125</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
@@ -4655,7 +4649,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4659,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LU0992631050</t>
+          <t>LU1299302684</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Carmignac Flexible Bond A EUR Ydis</t>
+          <t>Carmignac Flexible Bond A EUR Minc</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4689,7 +4683,13 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1090.800048828125</v>
+        <v>976.88</v>
+      </c>
+      <c r="H88" t="n">
+        <v>977.7005</v>
+      </c>
+      <c r="I88" t="n">
+        <v>38.06</v>
       </c>
       <c r="J88" s="1" t="inlineStr">
         <is>
@@ -4698,22 +4698,22 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>3</v>
+      <c r="A89" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LU1299302684</t>
+          <t>LU1317704135</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Carmignac Flexible Bond A EUR Minc</t>
+          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Obb. Misti</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>976.27</v>
+        <v>178.75</v>
       </c>
       <c r="H89" t="n">
-        <v>978.0105</v>
+        <v>178.0845</v>
       </c>
       <c r="I89" t="n">
-        <v>32.23</v>
+        <v>58.8</v>
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
@@ -4747,56 +4747,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-02-24 16:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>LU1317704135</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>178.94</v>
-      </c>
-      <c r="H90" t="n">
-        <v>178.009</v>
-      </c>
-      <c r="I90" t="n">
-        <v>61.96</v>
-      </c>
-      <c r="J90" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>2026-02-24 16:02</t>
+          <t>2026-02-26 19:47</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5115,6 +5066,65 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LU1623762843</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Carmignac Credit A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Altri</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>160.0200042724609</v>
+      </c>
+      <c r="H19" t="n">
+        <v>159.493</v>
+      </c>
+      <c r="I19" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Hang su FT Markets</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FR0010149302</t>
+          <t>FR0011269083</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carmignac Emergents A EUR Acc</t>
+          <t>Carmignac Sécurité AW EUR Ydis</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4177,59 +4177,65 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>Fondi Flessibili</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>99.56800079345703</v>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LU1317704051</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>1650.0419921875</v>
-      </c>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>3</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>FR0011269083</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Carmignac Sécurité AW EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Fondi Flessibili</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>99.56800079345703</v>
+        <v>190.63</v>
+      </c>
+      <c r="H78" t="n">
+        <v>189.8945</v>
+      </c>
+      <c r="I78" t="n">
+        <v>59.29</v>
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
@@ -4248,12 +4254,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FR0011269349</t>
+          <t>LU1163533349</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Carmignac Emergents A EUR Ydis</t>
+          <t>Carmignac Patrimoine E EUR Minc</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4263,7 +4269,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azionari Paesi Emergenti</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4272,7 +4278,13 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>215.6589965820312</v>
+        <v>69.37</v>
+      </c>
+      <c r="H79" t="n">
+        <v>68.967</v>
+      </c>
+      <c r="I79" t="n">
+        <v>54.11</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
@@ -4286,17 +4298,17 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n">
-        <v>2</v>
+      <c r="A80" t="n">
+        <v>3</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LU1317704051</t>
+          <t>FR0011269588</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
+          <t>Carmignac Patrimoine A EUR Ydis</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4306,7 +4318,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4315,13 +4327,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>190.63</v>
-      </c>
-      <c r="H80" t="n">
-        <v>189.8945</v>
-      </c>
-      <c r="I80" t="n">
-        <v>59.29</v>
+        <v>128.2530059814453</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -4340,12 +4346,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LU1163533349</t>
+          <t>LU1163533422</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine E EUR Minc</t>
+          <t>Carmignac Patrimoine A EUR Minc</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4364,13 +4370,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>69.37</v>
+        <v>73.19</v>
       </c>
       <c r="H81" t="n">
-        <v>68.967</v>
+        <v>72.76049999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>54.11</v>
+        <v>54.86</v>
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
@@ -4389,12 +4395,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FR0011269588</t>
+          <t>FR0010135103</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Ydis</t>
+          <t>Carmignac Patrimoine A EUR Acc</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4413,7 +4419,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>128.2530059814453</v>
+        <v>800.5250244140625</v>
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
@@ -4432,12 +4438,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LU1163533422</t>
+          <t>FR0010306142</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Minc</t>
+          <t>Carmignac Patrimoine E EUR Acc</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4447,7 +4453,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4456,13 +4462,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>73.19</v>
+        <v>192.75</v>
       </c>
       <c r="H83" t="n">
-        <v>72.76049999999999</v>
+        <v>191.6865</v>
       </c>
       <c r="I83" t="n">
-        <v>54.86</v>
+        <v>57.09</v>
       </c>
       <c r="J83" s="1" t="inlineStr">
         <is>
@@ -4481,12 +4487,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FR0010135103</t>
+          <t>LU0336084032</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Acc</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4496,7 +4502,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bilanciati</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4505,7 +4511,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>800.5250244140625</v>
+        <v>1380.400024414062</v>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
@@ -4524,12 +4530,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FR0010306142</t>
+          <t>LU0992631050</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine E EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Ydis</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4539,7 +4545,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bilanciati</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4548,13 +4554,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>192.75</v>
-      </c>
-      <c r="H85" t="n">
-        <v>191.6865</v>
-      </c>
-      <c r="I85" t="n">
-        <v>57.09</v>
+        <v>1090.800048828125</v>
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
@@ -4573,12 +4573,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LU0336084032</t>
+          <t>LU1299302684</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Carmignac Flexible Bond A EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Minc</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4597,7 +4597,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1380.400024414062</v>
+        <v>976.88</v>
+      </c>
+      <c r="H86" t="n">
+        <v>977.7005</v>
+      </c>
+      <c r="I86" t="n">
+        <v>38.06</v>
       </c>
       <c r="J86" s="1" t="inlineStr">
         <is>
@@ -4611,17 +4617,17 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>3</v>
+      <c r="A87" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LU0992631050</t>
+          <t>LU1317704135</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Carmignac Flexible Bond A EUR Ydis</t>
+          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4631,7 +4637,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Obb. Misti</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4640,7 +4646,13 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1090.800048828125</v>
+        <v>178.75</v>
+      </c>
+      <c r="H87" t="n">
+        <v>178.0845</v>
+      </c>
+      <c r="I87" t="n">
+        <v>58.8</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
@@ -4648,104 +4660,6 @@
         </is>
       </c>
       <c r="K87" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>3</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>LU1299302684</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Minc</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>976.88</v>
-      </c>
-      <c r="H88" t="n">
-        <v>977.7005</v>
-      </c>
-      <c r="I88" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>LU1317704135</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>178.75</v>
-      </c>
-      <c r="H89" t="n">
-        <v>178.0845</v>
-      </c>
-      <c r="I89" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
         <is>
           <t>2026-02-26 19:47</t>
         </is>
@@ -4762,7 +4676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5125,6 +5039,112 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FR0010149302</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Carmignac Emergents A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Altri</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1650.0419921875</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Hang FT Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FR0011269349</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Carmignac Emergents A EUR Ydis</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Azionari Paesi Emergenti</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>215.6589965820312</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Hang FT Markets</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
       <c r="I2" t="n">
         <v>71.08</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -592,7 +592,7 @@
       <c r="I3" t="n">
         <v>69.92</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -641,7 +641,7 @@
       <c r="I4" t="n">
         <v>70.58</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -690,7 +690,7 @@
       <c r="I5" t="n">
         <v>70.08</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -739,7 +739,7 @@
       <c r="I6" t="n">
         <v>49.53</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -788,7 +788,7 @@
       <c r="I7" t="n">
         <v>6.63</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -837,7 +837,7 @@
       <c r="I8" t="n">
         <v>74.39</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -886,7 +886,7 @@
       <c r="I9" t="n">
         <v>78.56</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -935,7 +935,7 @@
       <c r="I10" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -984,7 +984,7 @@
       <c r="I11" t="n">
         <v>68.19</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -1033,7 +1033,7 @@
       <c r="I12" t="n">
         <v>74.66</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -1082,7 +1082,7 @@
       <c r="I13" t="n">
         <v>64.3</v>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1094,7 +1094,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1131,7 +1131,7 @@
       <c r="I14" t="n">
         <v>62.47</v>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1180,7 +1180,7 @@
       <c r="I15" t="n">
         <v>55.14</v>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1229,7 +1229,7 @@
       <c r="I16" t="n">
         <v>52.97</v>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1278,7 +1278,7 @@
       <c r="I17" t="n">
         <v>55.4</v>
       </c>
-      <c r="J17" s="1" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1327,7 +1327,7 @@
       <c r="I18" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1376,7 +1376,7 @@
       <c r="I19" t="n">
         <v>72.56999999999999</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -1425,7 +1425,7 @@
       <c r="I20" t="n">
         <v>69.73999999999999</v>
       </c>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1474,7 +1474,7 @@
       <c r="I21" t="n">
         <v>61.47</v>
       </c>
-      <c r="J21" s="1" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1523,7 +1523,7 @@
       <c r="I22" t="n">
         <v>55.77</v>
       </c>
-      <c r="J22" s="1" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1535,7 +1535,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1572,7 +1572,7 @@
       <c r="I23" t="n">
         <v>57.83</v>
       </c>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1621,7 +1621,7 @@
       <c r="I24" t="n">
         <v>73.44</v>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1633,7 +1633,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1670,7 +1670,7 @@
       <c r="I25" t="n">
         <v>73.91</v>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -1719,7 +1719,7 @@
       <c r="I26" t="n">
         <v>54.83</v>
       </c>
-      <c r="J26" s="1" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1768,7 +1768,7 @@
       <c r="I27" t="n">
         <v>70.31</v>
       </c>
-      <c r="J27" s="1" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1817,7 +1817,7 @@
       <c r="I28" t="n">
         <v>81.16</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -1866,7 +1866,7 @@
       <c r="I29" t="n">
         <v>55.28</v>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1915,7 +1915,7 @@
       <c r="I30" t="n">
         <v>50.14</v>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -1927,7 +1927,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1964,7 +1964,7 @@
       <c r="I31" t="n">
         <v>35.5</v>
       </c>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2013,7 +2013,7 @@
       <c r="I32" t="n">
         <v>68.95</v>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2056,7 +2056,7 @@
       <c r="G33" t="n">
         <v>72.44599914550781</v>
       </c>
-      <c r="J33" s="1" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2068,7 +2068,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" t="n">
         <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2105,7 +2105,7 @@
       <c r="I34" t="n">
         <v>62.64</v>
       </c>
-      <c r="J34" s="1" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2154,7 +2154,7 @@
       <c r="I35" t="n">
         <v>58.56</v>
       </c>
-      <c r="J35" s="1" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2166,7 +2166,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" t="n">
         <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2203,7 +2203,7 @@
       <c r="I36" t="n">
         <v>45.48</v>
       </c>
-      <c r="J36" s="1" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2246,7 +2246,7 @@
       <c r="G37" t="n">
         <v>12.55599975585938</v>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2258,7 +2258,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" t="n">
         <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2295,7 +2295,7 @@
       <c r="I38" t="n">
         <v>63.5</v>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2344,7 +2344,7 @@
       <c r="I39" t="n">
         <v>36.64</v>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2393,7 +2393,7 @@
       <c r="I40" t="n">
         <v>70.62</v>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2442,7 +2442,7 @@
       <c r="I41" t="n">
         <v>100</v>
       </c>
-      <c r="J41" s="1" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2491,7 +2491,7 @@
       <c r="I42" t="n">
         <v>76.47</v>
       </c>
-      <c r="J42" s="1" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2540,7 +2540,7 @@
       <c r="I43" t="n">
         <v>73.76000000000001</v>
       </c>
-      <c r="J43" s="1" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2589,7 +2589,7 @@
       <c r="I44" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2638,7 +2638,7 @@
       <c r="I45" t="n">
         <v>70.97</v>
       </c>
-      <c r="J45" s="1" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2687,7 +2687,7 @@
       <c r="I46" t="n">
         <v>67.95999999999999</v>
       </c>
-      <c r="J46" s="1" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2736,7 +2736,7 @@
       <c r="I47" t="n">
         <v>88.51000000000001</v>
       </c>
-      <c r="J47" s="1" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2785,7 +2785,7 @@
       <c r="I48" t="n">
         <v>87.31</v>
       </c>
-      <c r="J48" s="1" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2834,7 +2834,7 @@
       <c r="I49" t="n">
         <v>68.13</v>
       </c>
-      <c r="J49" s="1" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2883,7 +2883,7 @@
       <c r="I50" t="n">
         <v>55.18</v>
       </c>
-      <c r="J50" s="1" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2932,7 +2932,7 @@
       <c r="I51" t="n">
         <v>68.39</v>
       </c>
-      <c r="J51" s="1" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -2981,7 +2981,7 @@
       <c r="I52" t="n">
         <v>51.08</v>
       </c>
-      <c r="J52" s="1" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3030,7 +3030,7 @@
       <c r="I53" t="n">
         <v>59.83</v>
       </c>
-      <c r="J53" s="1" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3079,7 +3079,7 @@
       <c r="I54" t="n">
         <v>79.70999999999999</v>
       </c>
-      <c r="J54" s="1" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3128,7 +3128,7 @@
       <c r="I55" t="n">
         <v>57.17</v>
       </c>
-      <c r="J55" s="1" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3177,7 +3177,7 @@
       <c r="I56" t="n">
         <v>62.67</v>
       </c>
-      <c r="J56" s="1" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3226,7 +3226,7 @@
       <c r="I57" t="n">
         <v>58.25</v>
       </c>
-      <c r="J57" s="1" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3275,7 +3275,7 @@
       <c r="I58" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="J58" s="1" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3324,7 +3324,7 @@
       <c r="I59" t="n">
         <v>57.58</v>
       </c>
-      <c r="J59" s="1" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3373,7 +3373,7 @@
       <c r="I60" t="n">
         <v>96.48999999999999</v>
       </c>
-      <c r="J60" s="1" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3422,7 +3422,7 @@
       <c r="I61" t="n">
         <v>81.06</v>
       </c>
-      <c r="J61" s="1" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3471,7 +3471,7 @@
       <c r="I62" t="n">
         <v>64.94</v>
       </c>
-      <c r="J62" s="1" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3520,7 +3520,7 @@
       <c r="I63" t="n">
         <v>63.81</v>
       </c>
-      <c r="J63" s="1" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3569,7 +3569,7 @@
       <c r="I64" t="n">
         <v>62.06</v>
       </c>
-      <c r="J64" s="1" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3618,7 +3618,7 @@
       <c r="I65" t="n">
         <v>71.58</v>
       </c>
-      <c r="J65" s="1" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3667,7 +3667,7 @@
       <c r="I66" t="n">
         <v>71.15000000000001</v>
       </c>
-      <c r="J66" s="1" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3716,7 +3716,7 @@
       <c r="I67" t="n">
         <v>69.03</v>
       </c>
-      <c r="J67" s="1" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3765,7 +3765,7 @@
       <c r="I68" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="J68" s="1" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3814,7 +3814,7 @@
       <c r="I69" t="n">
         <v>77.36</v>
       </c>
-      <c r="J69" s="1" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3863,7 +3863,7 @@
       <c r="I70" t="n">
         <v>30.23</v>
       </c>
-      <c r="J70" s="1" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3912,7 +3912,7 @@
       <c r="I71" t="n">
         <v>54.93</v>
       </c>
-      <c r="J71" s="1" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3961,7 +3961,7 @@
       <c r="I72" t="n">
         <v>46.8</v>
       </c>
-      <c r="J72" s="1" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -3978,12 +3978,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FR0010149120</t>
+          <t>FR0010312660</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carmignac Sécurité AW Cap EUR</t>
+          <t>Carmignac Investissement E EUR Acc</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Obb. Misti</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4002,9 +4002,15 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1926.787963867188</v>
-      </c>
-      <c r="J73" s="1" t="inlineStr">
+        <v>355.64</v>
+      </c>
+      <c r="H73" t="n">
+        <v>348.33</v>
+      </c>
+      <c r="I73" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4021,12 +4027,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FR0010312660</t>
+          <t>LU0336083810</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Carmignac Investissement E EUR Acc</t>
+          <t>Carmignac Asia Discovery A EUR Acc EUR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4036,7 +4042,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4045,15 +4051,9 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>355.64</v>
-      </c>
-      <c r="H74" t="n">
-        <v>348.33</v>
-      </c>
-      <c r="I74" t="n">
-        <v>61.47</v>
-      </c>
-      <c r="J74" s="1" t="inlineStr">
+        <v>2717.27099609375</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4066,16 +4066,16 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LU0336083810</t>
+          <t>FR0011269182</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Carmignac Asia Discovery A EUR Acc EUR</t>
+          <t>Carmignac Investissement A EUR Ydis</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azionari Paesi Emergenti</t>
+          <t>Azionari Internazionali</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4094,9 +4094,15 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2717.27099609375</v>
-      </c>
-      <c r="J75" s="1" t="inlineStr">
+        <v>279.91</v>
+      </c>
+      <c r="H75" t="n">
+        <v>278.601</v>
+      </c>
+      <c r="I75" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4108,17 +4114,17 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" t="n">
         <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FR0011269182</t>
+          <t>LU1317704051</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Carmignac Investissement A EUR Ydis</t>
+          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4128,7 +4134,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azionari Internazionali</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4137,15 +4143,15 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>279.91</v>
+        <v>190.63</v>
       </c>
       <c r="H76" t="n">
-        <v>278.601</v>
+        <v>189.8945</v>
       </c>
       <c r="I76" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="J76" s="1" t="inlineStr">
+        <v>59.29</v>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4162,12 +4168,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FR0011269083</t>
+          <t>LU1163533349</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carmignac Sécurité AW EUR Ydis</t>
+          <t>Carmignac Patrimoine E EUR Minc</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4177,7 +4183,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fondi Flessibili</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4186,9 +4192,15 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>99.56800079345703</v>
-      </c>
-      <c r="J77" s="1" t="inlineStr">
+        <v>69.37</v>
+      </c>
+      <c r="H77" t="n">
+        <v>68.967</v>
+      </c>
+      <c r="I77" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4200,17 +4212,17 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n">
-        <v>2</v>
+      <c r="A78" t="n">
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LU1317704051</t>
+          <t>FR0011269588</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
+          <t>Carmignac Patrimoine A EUR Ydis</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4220,7 +4232,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4229,15 +4241,9 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>190.63</v>
-      </c>
-      <c r="H78" t="n">
-        <v>189.8945</v>
-      </c>
-      <c r="I78" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="J78" s="1" t="inlineStr">
+        <v>128.2530059814453</v>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4254,12 +4260,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LU1163533349</t>
+          <t>LU1163533422</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine E EUR Minc</t>
+          <t>Carmignac Patrimoine A EUR Minc</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4278,15 +4284,15 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>69.37</v>
+        <v>73.19</v>
       </c>
       <c r="H79" t="n">
-        <v>68.967</v>
+        <v>72.76049999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="J79" s="1" t="inlineStr">
+        <v>54.86</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4303,12 +4309,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FR0011269588</t>
+          <t>FR0010135103</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Ydis</t>
+          <t>Carmignac Patrimoine A EUR Acc</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4327,9 +4333,9 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>128.2530059814453</v>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
+        <v>800.5250244140625</v>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4346,12 +4352,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LU1163533422</t>
+          <t>FR0010306142</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Minc</t>
+          <t>Carmignac Patrimoine E EUR Acc</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4361,7 +4367,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Altri</t>
+          <t>Bilanciati</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4370,15 +4376,15 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>73.19</v>
+        <v>192.75</v>
       </c>
       <c r="H81" t="n">
-        <v>72.76049999999999</v>
+        <v>191.6865</v>
       </c>
       <c r="I81" t="n">
-        <v>54.86</v>
-      </c>
-      <c r="J81" s="1" t="inlineStr">
+        <v>57.09</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4395,12 +4401,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FR0010135103</t>
+          <t>LU0336084032</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine A EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Acc</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4410,7 +4416,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bilanciati</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4419,9 +4425,9 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>800.5250244140625</v>
-      </c>
-      <c r="J82" s="1" t="inlineStr">
+        <v>1380.400024414062</v>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4438,12 +4444,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FR0010306142</t>
+          <t>LU0992631050</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Carmignac Patrimoine E EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Ydis</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4453,7 +4459,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bilanciati</t>
+          <t>Obb. Misti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4462,15 +4468,9 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>192.75</v>
-      </c>
-      <c r="H83" t="n">
-        <v>191.6865</v>
-      </c>
-      <c r="I83" t="n">
-        <v>57.09</v>
-      </c>
-      <c r="J83" s="1" t="inlineStr">
+        <v>1090.800048828125</v>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LU0336084032</t>
+          <t>LU1299302684</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Carmignac Flexible Bond A EUR Acc</t>
+          <t>Carmignac Flexible Bond A EUR Minc</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4511,9 +4511,15 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1380.400024414062</v>
-      </c>
-      <c r="J84" s="1" t="inlineStr">
+        <v>976.88</v>
+      </c>
+      <c r="H84" t="n">
+        <v>977.7005</v>
+      </c>
+      <c r="I84" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4526,16 +4532,16 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LU0992631050</t>
+          <t>LU1317704135</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Carmignac Flexible Bond A EUR Ydis</t>
+          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4545,7 +4551,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Obb. Misti</t>
+          <t>Altri</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4554,112 +4560,20 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1090.800048828125</v>
-      </c>
-      <c r="J85" s="1" t="inlineStr">
+        <v>178.75</v>
+      </c>
+      <c r="H85" t="n">
+        <v>178.0845</v>
+      </c>
+      <c r="I85" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>LU1299302684</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Minc</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>976.88</v>
-      </c>
-      <c r="H86" t="n">
-        <v>977.7005</v>
-      </c>
-      <c r="I86" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>LU1317704135</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>178.75</v>
-      </c>
-      <c r="H87" t="n">
-        <v>178.0845</v>
-      </c>
-      <c r="I87" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
         <is>
           <t>2026-02-26 19:47</t>
         </is>
@@ -4676,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5145,6 +5059,92 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FR0010149120</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Carmignac Sécurité AW Cap EUR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Obb. Misti</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1926.787963867188</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FR0011269083</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Carmignac Sécurité AW EUR Ydis</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Fondi Flessibili</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>99.56800079345703</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4157,423 +4157,6 @@
         </is>
       </c>
       <c r="K76" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>3</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>LU1163533349</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine E EUR Minc</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>69.37</v>
-      </c>
-      <c r="H77" t="n">
-        <v>68.967</v>
-      </c>
-      <c r="I77" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>3</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>FR0011269588</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine A EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Bilanciati</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>128.2530059814453</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>3</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>LU1163533422</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine A EUR Minc</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>73.19</v>
-      </c>
-      <c r="H79" t="n">
-        <v>72.76049999999999</v>
-      </c>
-      <c r="I79" t="n">
-        <v>54.86</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>3</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>FR0010135103</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Bilanciati</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>800.5250244140625</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>3</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>FR0010306142</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Carmignac Patrimoine E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Bilanciati</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>192.75</v>
-      </c>
-      <c r="H81" t="n">
-        <v>191.6865</v>
-      </c>
-      <c r="I81" t="n">
-        <v>57.09</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>3</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>LU0336084032</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Acc</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>1380.400024414062</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>3</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>LU0992631050</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Ydis</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>1090.800048828125</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>LU1299302684</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Carmignac Flexible Bond A EUR Minc</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Obb. Misti</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>976.88</v>
-      </c>
-      <c r="H84" t="n">
-        <v>977.7005</v>
-      </c>
-      <c r="I84" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>2</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>LU1317704135</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Carmignac</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Altri</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>178.75</v>
-      </c>
-      <c r="H85" t="n">
-        <v>178.0845</v>
-      </c>
-      <c r="I85" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
         <is>
           <t>2026-02-26 19:47</t>
         </is>
@@ -4590,7 +4173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5145,6 +4728,423 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LU1163533349</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Carmignac Patrimoine E EUR Minc</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Altri</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="H24" t="n">
+        <v>68.967</v>
+      </c>
+      <c r="I24" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FR0011269588</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Carmignac Patrimoine A EUR Ydis</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bilanciati</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>128.2530059814453</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LU1163533422</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Carmignac Patrimoine A EUR Minc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Altri</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="H26" t="n">
+        <v>72.76049999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FR0010135103</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Carmignac Patrimoine A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bilanciati</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>800.5250244140625</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FR0010306142</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Carmignac Patrimoine E EUR Acc</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bilanciati</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>192.75</v>
+      </c>
+      <c r="H28" t="n">
+        <v>191.6865</v>
+      </c>
+      <c r="I28" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LU0336084032</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Carmignac Flexible Bond A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Obb. Misti</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1380.400024414062</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LU0992631050</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Carmignac Flexible Bond A EUR Ydis</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Obb. Misti</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1090.800048828125</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LU1299302684</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Carmignac Flexible Bond A EUR Minc</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Obb. Misti</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>976.88</v>
+      </c>
+      <c r="H31" t="n">
+        <v>977.7005</v>
+      </c>
+      <c r="I31" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LU1317704135</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Carmignac</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Altri</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="H32" t="n">
+        <v>178.0845</v>
+      </c>
+      <c r="I32" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Fondi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fondi_Rimossi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="idx" hidden="0" function="0" vbProcedure="0">Fondi!$C$86</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -77,7 +79,10 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -358,3830 +363,4126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="28.23" customWidth="1" style="3" min="2" max="2"/>
-    <col width="45.14" customWidth="1" style="3" min="3" max="3"/>
-    <col width="34.26" customWidth="1" style="3" min="4" max="4"/>
-    <col width="34.11" customWidth="1" style="3" min="5" max="5"/>
+    <col width="28.23" customWidth="1" style="4" min="2" max="2"/>
+    <col width="54.56" customWidth="1" style="4" min="3" max="3"/>
+    <col width="34.26" customWidth="1" style="4" min="4" max="4"/>
+    <col width="34.11" customWidth="1" style="4" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="5">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Livello</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Nome Fondo</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Casa Gestione</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Prezzo</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>MM15</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Segnale</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Ultima Modifica</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="4">
-      <c r="A2" s="3" t="n">
+    <row r="2" ht="15" customHeight="1" s="5">
+      <c r="A2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>LU1548497772</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Allianz Global Artificial Intelligence AT H2-EUR</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Allianz</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>296.91</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>289.2315</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>71.08</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="3" t="n">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="5">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>LU0273159177</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>DWS Invest Gold and Precious Metals Equities LC</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>DWS</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>380.52</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>355.4335</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>69.92</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="3" t="n">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="5">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>LU0273148055</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>DWS Invest Gold and Precious Metals Equities NC</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>DWS</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>325.2</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>303.791</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <v>70.58</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="3" t="n">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="5">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>LU0208853944</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>JPM Global Natural Resources (EUR) D Acc</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>19.23</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>18.563</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>70.08</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="4">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="5">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>LU0173785626</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Nordea 1 - Swedish Short-Term Bond Fund BP Acc</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Breve Termine</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>20.04</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>20.0695</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <v>49.53</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="4">
-      <c r="A7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="5">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>LU2357810188</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Amundi S.F. - Diversified Short-Term Bond Select A EUR AD</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Breve Termine</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>51.08</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>51.951</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <v>6.63</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="4">
-      <c r="A8" s="3" t="n">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="5">
+      <c r="A8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>LU1046235815</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Schroder ISF Strategic Credit B EUR Hedged Acc</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Schroders</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Corporate</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>125.72</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <v>125.6435</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <v>74.39</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="4">
-      <c r="A9" s="3" t="n">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="5">
+      <c r="A9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>LU1046236037</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Schroder ISF Strategic Credit A EUR Hedged Inc</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Schroders</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Corporate</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>94.97</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>94.9025</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="4" t="n">
         <v>78.56</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="4">
-      <c r="A10" s="3" t="n">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="5">
+      <c r="A10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>IT0004782758</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Eurizon Obbligazioni Euro Breve Term A</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Eurizon</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Euro</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>17.14</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>17.1275</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="4" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="3" t="n">
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="5">
+      <c r="A11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>LU0430494962</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>JPM Global Short Duration Bond Fund A (acc) EUR hedged</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Breve Termine</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>7.68</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>7.6755</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <v>68.19</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="4">
-      <c r="A12" s="3" t="n">
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="5">
+      <c r="A12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>LU0408876448</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>JPM Global Government Short Duration Bond A (acc) EUR</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Governativi</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>10.83</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>10.826</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>74.66</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="4">
-      <c r="A13" s="3" t="n">
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="5">
+      <c r="A13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>LU1915690595</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Nordea 1 - Active Rates Opportunities Fund BP EUR</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Flessibili</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>123.11</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>122.947</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="4" t="n">
         <v>64.3</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="4">
-      <c r="A14" s="3" t="n">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="5">
+      <c r="A14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>LU0165520114</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Candriam Bonds Global Inflation Short duration Classic C Acc</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Candriam</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari Inflation Linked</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>149.73</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>149.561</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="4" t="n">
         <v>62.47</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="4">
-      <c r="A15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="5">
+      <c r="A15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>LU1213836080</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Global Technology Fund A-ACC-EUR</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>58.06</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <v>57.393</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="4" t="n">
         <v>55.14</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="4">
-      <c r="A16" s="3" t="n">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="5">
+      <c r="A16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>IE000RHGM613</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Nbg Bm Nex Gen Spc Ecy EUR M Acc Unh</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>NBG Asset Management</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Azionari Tematici</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>22.53</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="4" t="n">
         <v>22.387</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" s="4" t="n">
         <v>52.97</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="4">
-      <c r="A17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="5">
+      <c r="A17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>LU2484078832</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Invesco Funds - Invesco Metaverse and AI Fund A Acc EUR</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Invesco</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>18.78</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="4" t="n">
         <v>18.1005</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" s="4" t="n">
         <v>55.4</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="5">
+      <c r="A18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>LU0115773425</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>FF - Global Technology Fund - E - ACC - Euro</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>73.39</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="4" t="n">
         <v>72.5565</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="4">
-      <c r="A19" s="3" t="n">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="5">
+      <c r="A19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>LU1213835942</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Latin America Fund A-ACC-EUR</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Azionari America Latina</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>15.57</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="4" t="n">
         <v>15.0735</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="4" t="n">
         <v>72.56999999999999</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="4">
-      <c r="A20" s="3" t="n">
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="5">
+      <c r="A20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>LU0309468808</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Nordea-1 Latin American Eq BP Acc</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Azionari America Latina</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
         <v>20.19</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="4" t="n">
         <v>19.8565</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="4" t="n">
         <v>69.73999999999999</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="4">
-      <c r="A21" s="3" t="n">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="5">
+      <c r="A21" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>LU0522352862</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - JPM Latin America Equity D (acc) - EUR</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Azionari America Latina</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>115.37</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="4" t="n">
         <v>114.5695</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="4" t="n">
         <v>61.47</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="4">
-      <c r="A22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="5">
+      <c r="A22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>LU0326424115</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>BlackRock Global Funds - World Mining Fund A2 EUR Hedged</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>BlackRock</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>8.48</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" s="4" t="n">
         <v>7.9335</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" s="4" t="n">
         <v>55.77</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="4">
-      <c r="A23" s="3" t="n">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="5">
+      <c r="A23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>LU0106817157</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Schroder ISF Emerg Eur A Acc</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Schroders</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Azionari Europa Emergente</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>32.71</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="4" t="n">
         <v>32.5935</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="4" t="n">
         <v>57.83</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="4">
-      <c r="A24" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="5">
+      <c r="A24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>LU0326422176</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>BlackRock Global Funds - World Energy Fund A2 EUR Hedged</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>BlackRock</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Azionari Energia</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>7.57</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="4" t="n">
         <v>7.2805</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="4" t="n">
         <v>73.44</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="4">
-      <c r="A25" s="3" t="n">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="5">
+      <c r="A25" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>LU0056052961</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Candriam Equities L Emerging Markets C EUR Acc</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Candriam</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Azionari Mercati Emergenti</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>1410.59</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="4" t="n">
         <v>1350.6905</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" s="4" t="n">
         <v>73.91</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="4">
-      <c r="A26" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="5">
+      <c r="A26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>IE00BGMHJH08</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Amundi Alternative Funds II PLC - Amundi Marathon Emerging Markets Bond Fund A EUR Acc</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Azionari Europa/Africa/ME</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>101.24</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="4" t="n">
         <v>33.9061</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="4" t="n">
         <v>54.83</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="4">
-      <c r="A27" s="3" t="n">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="5">
+      <c r="A27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>LU0303816028</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Emerging Europe, Middle East and Africa A Euro</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Azionari Europa/Africa/ME</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n">
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>19.32</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="4" t="n">
         <v>18.9775</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" s="4" t="n">
         <v>70.31</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="4">
-      <c r="A28" s="3" t="n">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="5">
+      <c r="A28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>LU0307839646</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Emerging Markets A Euro</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Azionari Mercati Emergenti</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="4" t="n">
         <v>21.7815</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="4" t="n">
         <v>81.16</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="4">
-      <c r="A29" s="3" t="n">
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="5">
+      <c r="A29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>LU0114720955</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Global Health Care A EUR</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Azionari Salute/Pharma</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>62.66</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="4" t="n">
         <v>62.26</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" s="4" t="n">
         <v>55.28</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="4">
-      <c r="A30" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="5">
+      <c r="A30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>LU0880062913</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Global Healthcare Fund A (acc) - EUR</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Azionari Salute/Pharma</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
         <v>283.65</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" s="4" t="n">
         <v>281.0385</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" s="4" t="n">
         <v>50.14</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="4">
-      <c r="A31" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="5">
+      <c r="A31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>LU1391767586</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Global Financial Services Fund A-Acc-EUR</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Azionari Finanziari</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
         <v>25.14</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" s="4" t="n">
         <v>25.655</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="4" t="n">
         <v>35.5</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="4">
-      <c r="A32" s="3" t="n">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="5">
+      <c r="A32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>LU0210527791</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Europe Equity A EUR</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Azionari Finanziari</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
         <v>32.6199989318848</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="4" t="n">
         <v>31.8945</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="4" t="n">
         <v>68.95</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="4">
-      <c r="A33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="5">
+      <c r="A33" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>LU0640476718</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Sustainable Consumer Brands A EUR</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Azionari Consumi/Lusso</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
         <v>72.4459991455078</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="4">
-      <c r="A34" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="5">
+      <c r="A34" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>LU0069450822</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - America Fund A EUR</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Azionari USA</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
         <v>16.07</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="4" t="n">
         <v>15.9835</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="4" t="n">
         <v>62.64</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="4">
-      <c r="A35" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="5">
+      <c r="A35" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>LU1706106447</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Nordea 1 - European Sustainable Stars Equity BP EUR</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
         <v>204.84</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="4" t="n">
         <v>200.7005</v>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" s="4" t="n">
         <v>58.56</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="4">
-      <c r="A36" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="5">
+      <c r="A36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>LU0261959422</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - European Dynamic Growth Fund A-Acc-EUR</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
         <v>32.25</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="H36" s="4" t="n">
         <v>31.87</v>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" s="4" t="n">
         <v>45.48</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="4">
-      <c r="A37" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="5">
+      <c r="A37" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>LU0048597586</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - Asia Focus A EUR</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Azionari Asia Pacifico</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="n">
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>12.5559997558594</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="4">
-      <c r="A38" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="5">
+      <c r="A38" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>LU2401078998</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Nordea 1 - Global Sustainable Stars Equity Fund AF EUR</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Azionari Globali</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
         <v>246.09</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="4" t="n">
         <v>240.2335</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="4" t="n">
         <v>63.5</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="4">
-      <c r="A39" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="5">
+      <c r="A39" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>LU1269890163</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Candriam Bonds Euro High Yield Class C (Q) EUR Dis</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Candriam</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Obbligazionari High Yield</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n">
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
         <v>157.03</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="4" t="n">
         <v>157.212</v>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="4" t="n">
         <v>36.64</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="4">
-      <c r="A40" s="3" t="n">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="5">
+      <c r="A40" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>FR0010510800</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Amundi Fds - Euro Government Bond A EUR C</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Monetari Euro</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n">
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
         <v>113.161003112793</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="4" t="n">
         <v>113.0768</v>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" s="4" t="n">
         <v>70.62</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="4">
-      <c r="A41" s="3" t="n">
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="5">
+      <c r="A41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>LU0568621618</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Euro Government Liquidity A EUR</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Monetari Euro</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
         <v>128.860000610352</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="4" t="n">
         <v>128.617</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="4">
-      <c r="A42" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="5">
+      <c r="A42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>LU0987184941</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Absolute Return Forex R EUR (C)</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Fondi Flessibili</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n">
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
         <v>103.65</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="H42" s="4" t="n">
         <v>103.392</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" s="4" t="n">
         <v>76.47</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="4">
-      <c r="A43" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="5">
+      <c r="A43" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>LU0557854147</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Asia Equity Focus A EUR (C)</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Azionari Pacifico</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
         <v>232.15</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="4" t="n">
         <v>219.028</v>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="I43" s="4" t="n">
         <v>73.76000000000001</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="4">
-      <c r="A44" s="3" t="n">
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="5">
+      <c r="A44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>LU0568620560</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Amundi F. Cash EUR A2 EUR</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Fondi di Mercato Monetario Euro</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
         <v>106.15</v>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="H44" s="4" t="n">
         <v>106.1105</v>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="4">
-      <c r="A45" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="5">
+      <c r="A45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>LU2386146430</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Emerging Markets Equity Select A2 EUR (C)</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
         <v>84.08</v>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="4" t="n">
         <v>79.8175</v>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" s="4" t="n">
         <v>70.97</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="4">
-      <c r="A46" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="5">
+      <c r="A46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>LU0568583420</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Equity Japan Target A EUR (C)</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Azionari Paese</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
         <v>329.51</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="4" t="n">
         <v>316.654</v>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" s="4" t="n">
         <v>67.95999999999999</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="4">
-      <c r="A47" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="5">
+      <c r="A47" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>LU0616241476</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Euro Aggregate Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Obb. Altre Special.</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="n">
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
         <v>134.6</v>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="4" t="n">
         <v>133.8405</v>
       </c>
-      <c r="I47" s="3" t="n">
+      <c r="I47" s="4" t="n">
         <v>88.51000000000001</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="4">
-      <c r="A48" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="5">
+      <c r="A48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>LU0518421895</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Euro Government Bond Responsible A EUR (C)</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Obb. Euro Governativi M/L Termine</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="n">
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
         <v>125.16</v>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="H48" s="4" t="n">
         <v>124.201</v>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I48" s="4" t="n">
         <v>87.31</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="4">
-      <c r="A49" s="3" t="n">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="5">
+      <c r="A49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>LU1883303551</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Euroland Equity A CHF Hgd (C)</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Azionari Area Euro</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n">
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
         <v>111.459999084473</v>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" s="4" t="n">
         <v>109.2185</v>
       </c>
-      <c r="I49" s="3" t="n">
+      <c r="I49" s="4" t="n">
         <v>68.13</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="4">
-      <c r="A50" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="5">
+      <c r="A50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>LU0568607203</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Euroland Equity Small Cap Select A EUR (C)</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Azionari Area Euro</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="n">
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
         <v>260.57</v>
       </c>
-      <c r="H50" s="3" t="n">
+      <c r="H50" s="4" t="n">
         <v>256.88</v>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" s="4" t="n">
         <v>55.18</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="4">
-      <c r="A51" s="3" t="n">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="5">
+      <c r="A51" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>LU1883310846</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Europe Equity Income Select A2 AUD H QTI D</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
         <v>56.060001373291</v>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="4" t="n">
         <v>55.1783</v>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="I51" s="4" t="n">
         <v>68.39</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="4">
-      <c r="A52" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="5">
+      <c r="A52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>LU1883306497</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - European Equity Small Cap A EUR (C)</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="n">
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
         <v>222.52</v>
       </c>
-      <c r="H52" s="3" t="n">
+      <c r="H52" s="4" t="n">
         <v>221.319</v>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="I52" s="4" t="n">
         <v>51.08</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="4">
-      <c r="A53" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="5">
+      <c r="A53" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>LU3081003082</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Absolute Return Global Opportunities Bond A EUR MTD D</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Obb. Altre Special.</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="n">
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
         <v>50.47</v>
       </c>
-      <c r="H53" s="3" t="n">
+      <c r="H53" s="4" t="n">
         <v>50.3505</v>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="I53" s="4" t="n">
         <v>59.83</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="4">
-      <c r="A54" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="5">
+      <c r="A54" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>LU2330497517</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Corporate Bond Select A2 EUR Hedged Acc</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Obb. Intern. Corporate Investment Grade</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="n">
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
         <v>46.93</v>
       </c>
-      <c r="H54" s="3" t="n">
+      <c r="H54" s="4" t="n">
         <v>46.734</v>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="I54" s="4" t="n">
         <v>79.70999999999999</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="4">
-      <c r="A55" s="3" t="n">
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="5">
+      <c r="A55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>LU2531474588</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds Global Equity Climate A USD Capitalisation</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Azionari Internazionali</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="n">
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
         <v>87.5500030517578</v>
       </c>
-      <c r="H55" s="3" t="n">
+      <c r="H55" s="4" t="n">
         <v>87.523</v>
       </c>
-      <c r="I55" s="3" t="n">
+      <c r="I55" s="4" t="n">
         <v>57.17</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="4">
-      <c r="A56" s="3" t="n">
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="5">
+      <c r="A56" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>LU1883318666</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Equity Responsible A CHF (C)</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Azionari Altri Settori</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="n">
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
         <v>484.470001220703</v>
       </c>
-      <c r="H56" s="3" t="n">
+      <c r="H56" s="4" t="n">
         <v>477.475</v>
       </c>
-      <c r="I56" s="3" t="n">
+      <c r="I56" s="4" t="n">
         <v>62.67</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="4">
-      <c r="A57" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="5">
+      <c r="A57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>LU1162499526</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Global High Yield Bond A EUR Hgd (C)</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Obb. Dollaro High Yield</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="n">
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>114.15</v>
       </c>
-      <c r="H57" s="3" t="n">
+      <c r="H57" s="4" t="n">
         <v>113.925</v>
       </c>
-      <c r="I57" s="3" t="n">
+      <c r="I57" s="4" t="n">
         <v>58.25</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="4">
-      <c r="A58" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="5">
+      <c r="A58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>LU0442405998</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Inflation Short Duration Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Obb. Intern. Governativi</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="n">
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
         <v>105.21</v>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="H58" s="4" t="n">
         <v>105.189</v>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="I58" s="4" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="4">
-      <c r="A59" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="5">
+      <c r="A59" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>LU1883327907</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Multi-Asset A USD (C)</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Bilanciati Obbligazionari</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="n">
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
         <v>170.660003662109</v>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="H59" s="4" t="n">
         <v>169.8945</v>
       </c>
-      <c r="I59" s="3" t="n">
+      <c r="I59" s="4" t="n">
         <v>57.58</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="4">
-      <c r="A60" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="5">
+      <c r="A60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>LU1883334275</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Subordinated Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Obb. Altre Special.</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="n">
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
         <v>75.26000000000001</v>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="H60" s="4" t="n">
         <v>75.00149999999999</v>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I60" s="4" t="n">
         <v>96.48999999999999</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="4">
-      <c r="A61" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="5">
+      <c r="A61" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>LU0945151578</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Impact Euro Corporate Short Term Green Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Obb. Euro Corporate Investment Grade</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="n">
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
         <v>105.99</v>
       </c>
-      <c r="H61" s="3" t="n">
+      <c r="H61" s="4" t="n">
         <v>105.9255</v>
       </c>
-      <c r="I61" s="3" t="n">
+      <c r="I61" s="4" t="n">
         <v>81.06</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="4">
-      <c r="A62" s="3" t="n">
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="5">
+      <c r="A62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>LU2585853059</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Income Opportunities A2 AUD H MTD3 (D)</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Fondi Flessibili</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="n">
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
         <v>56.4099998474121</v>
       </c>
-      <c r="H62" s="3" t="n">
+      <c r="H62" s="4" t="n">
         <v>56.2893</v>
       </c>
-      <c r="I62" s="3" t="n">
+      <c r="I62" s="4" t="n">
         <v>64.94</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="4">
-      <c r="A63" s="3" t="n">
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="5">
+      <c r="A63" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>LU1923161894</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Japan Equity Select A USD (C)</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>Azionari Pacifico</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="n">
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
         <v>80.620002746582</v>
       </c>
-      <c r="H63" s="3" t="n">
+      <c r="H63" s="4" t="n">
         <v>77.80200000000001</v>
       </c>
-      <c r="I63" s="3" t="n">
+      <c r="I63" s="4" t="n">
         <v>63.81</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="4">
-      <c r="A64" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="5">
+      <c r="A64" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>LU0552029406</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Latin America Equity A EUR (C)</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="n">
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
         <v>128.36</v>
       </c>
-      <c r="H64" s="3" t="n">
+      <c r="H64" s="4" t="n">
         <v>123.431</v>
       </c>
-      <c r="I64" s="3" t="n">
+      <c r="I64" s="4" t="n">
         <v>62.06</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="4">
-      <c r="A65" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="5">
+      <c r="A65" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>LU1883336569</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Optimal Yield A EUR (C)</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Obb. Flessibili</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="n">
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
         <v>118.01</v>
       </c>
-      <c r="H65" s="3" t="n">
+      <c r="H65" s="4" t="n">
         <v>117.8</v>
       </c>
-      <c r="I65" s="3" t="n">
+      <c r="I65" s="4" t="n">
         <v>71.58</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="4">
-      <c r="A66" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="5">
+      <c r="A66" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>LU1883339233</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Optimal Yield Short Term A EUR (C)</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Obb. Flessibili</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="n">
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
         <v>58.78</v>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="H66" s="4" t="n">
         <v>58.682</v>
       </c>
-      <c r="I66" s="3" t="n">
+      <c r="I66" s="4" t="n">
         <v>71.15000000000001</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="4">
-      <c r="A67" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="5">
+      <c r="A67" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>LU1880401101</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - US Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Obb. Dollaro Governativi M/L Termine</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="n">
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
         <v>53.03</v>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="H67" s="4" t="n">
         <v>52.463</v>
       </c>
-      <c r="I67" s="3" t="n">
+      <c r="I67" s="4" t="n">
         <v>69.03</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="4">
-      <c r="A68" s="3" t="n">
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="5">
+      <c r="A68" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>LU2559893917</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - US Corporate Bond Climate A USD (C)</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="n">
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
         <v>58.0699996948242</v>
       </c>
-      <c r="H68" s="3" t="n">
+      <c r="H68" s="4" t="n">
         <v>57.7105</v>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="I68" s="4" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="4">
-      <c r="A69" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="5">
+      <c r="A69" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>LU3238210200</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - US Corporate Bond Select A EUR Hgd AD (D)</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>Obb. Dollaro Corporate Investment Grade</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="n">
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
         <v>50.6</v>
       </c>
-      <c r="H69" s="3" t="n">
+      <c r="H69" s="4" t="n">
         <v>50.331</v>
       </c>
-      <c r="I69" s="3" t="n">
+      <c r="I69" s="4" t="n">
         <v>77.36</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="4">
-      <c r="A70" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="5">
+      <c r="A70" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>LU1883854199</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - US Equity Fundamental Growth A EUR C</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Azionari America</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="n">
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
         <v>562.75</v>
       </c>
-      <c r="H70" s="3" t="n">
+      <c r="H70" s="4" t="n">
         <v>567.1135</v>
       </c>
-      <c r="I70" s="3" t="n">
+      <c r="I70" s="4" t="n">
         <v>30.23</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="4">
-      <c r="A71" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="5">
+      <c r="A71" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>LU1883859230</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - US Equity Research A EUR (C)</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>Azionari America</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
         <v>24.59</v>
       </c>
-      <c r="H71" s="3" t="n">
+      <c r="H71" s="4" t="n">
         <v>23.984</v>
       </c>
-      <c r="I71" s="3" t="n">
+      <c r="I71" s="4" t="n">
         <v>54.93</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="4">
-      <c r="A72" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="5">
+      <c r="A72" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>LU2146567529</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - US Equity Select A EUR (C)</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>Azionari America</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="n">
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
         <v>81.53</v>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="H72" s="4" t="n">
         <v>81.0485</v>
       </c>
-      <c r="I72" s="3" t="n">
+      <c r="I72" s="4" t="n">
         <v>46.8</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="4">
-      <c r="A73" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="5">
+      <c r="A73" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>FR0010312660</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Carmignac Investissement E EUR Acc</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="n">
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
         <v>355.64</v>
       </c>
-      <c r="H73" s="3" t="n">
+      <c r="H73" s="4" t="n">
         <v>348.33</v>
       </c>
-      <c r="I73" s="3" t="n">
+      <c r="I73" s="4" t="n">
         <v>61.47</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="4">
-      <c r="A74" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="5">
+      <c r="A74" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>LU0336083810</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Carmignac Asia Discovery A EUR Acc EUR</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="n">
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
         <v>2717.27099609375</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="4">
-      <c r="A75" s="3" t="n">
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="5">
+      <c r="A75" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>FR0011269182</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Carmignac Investissement A EUR Ydis</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Azionari Internazionali</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n">
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
         <v>279.91</v>
       </c>
-      <c r="H75" s="3" t="n">
+      <c r="H75" s="4" t="n">
         <v>278.601</v>
       </c>
-      <c r="I75" s="3" t="n">
+      <c r="I75" s="4" t="n">
         <v>47.36</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="4">
-      <c r="A76" s="3" t="n">
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="5">
+      <c r="A76" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>LU1317704051</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="n">
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
         <v>190.63</v>
       </c>
-      <c r="H76" s="3" t="n">
+      <c r="H76" s="4" t="n">
         <v>189.8945</v>
       </c>
-      <c r="I76" s="3" t="n">
+      <c r="I76" s="4" t="n">
         <v>59.29</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="4">
-      <c r="A77" t="n">
-        <v>3</v>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="5">
+      <c r="A77" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>LU1861216783</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>BGF Next Generation Technology E2 Cap EUR Hdg</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Blackrock Global Funds SICAV</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>Azionari Altri Settori</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="n">
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
         <v>21.24</v>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="4">
-      <c r="A78" t="n">
-        <v>3</v>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
+    <row r="78" ht="15" customHeight="1" s="5">
+      <c r="A78" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>LU0705071453</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>RAM (Lux) SF European Market Neutral Eq.B EUR</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>RAM (Lux) Systematic Funds</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="n">
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
         <v>184.09</v>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="4">
-      <c r="A79" t="n">
-        <v>3</v>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="5">
+      <c r="A79" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>LU1176912761</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>JPM Europe Eq. Absolute Alpha D (perf) Acc EUR</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>JP Morgan Funds SICAV</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="n">
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="n">
         <v>155.39</v>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="4"/>
-    <row r="1048576" ht="12.8" customHeight="1" s="4"/>
+    <row r="80" ht="15" customHeight="1" s="5">
+      <c r="A80" t="n">
+        <v>3</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>IE00B79S1F56</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Pimco Commodities Plus Strategy Fund Classe E Eur Hdg</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Pimco Funds Global Investors Series PLC</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="5">
+      <c r="A81" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>LU1106545376</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Vontobel Fund - Non-Food Commodity Classe H EUR Acc</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Vontobel Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>100.46</v>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="5">
+      <c r="A82" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>AT0000688684</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Raiffeisen Azionario Energia (r)</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Raiffeisen Kapitalanlage Gesellschaft</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Energia</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>220.12</v>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" s="5">
+      <c r="A83" t="n">
+        <v>3</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>LU0757427116</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Threadneedle (Lux) - Enhanced Commodities Fund Classe AU EUR</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Columbia Threadneedle (Lux) I</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>Ritorno Assoluto Materie Prime</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>16.23</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="5">
+      <c r="A84" t="n">
+        <v>3</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>LU0273974336</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Amundi S.F. - EUR Commodities Classe F EUR Acc</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Amundi SF SICAV</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Ritorno Assoluto Materie Prime</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="5">
+      <c r="A85" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>LU0173784223</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Nordea 1 - Norwegian Equity Fund Classe BP Eur</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Nordea 1 SICAV</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Azionari Norvegia</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>44.82</v>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="5">
+      <c r="A86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>LU0173770354</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Nordea 1 - Norwegian Equity Fund Classe E Eur (acc)</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Nordea 1 SICAV</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Azionari Norvegia</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="5">
+      <c r="A87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>IE00BLLXH031</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Neu.Berman 5G Connectivity Classe M Eur Acc</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Neuberger Berman Europe</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Telecomunicazioni</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>20.84</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="5">
+      <c r="A88" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>LU1881514001</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>FF - Future Connectivity Fund Classe A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Fidelity Funds SICAV</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Telecomunicazioni</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>20.74</v>
+      </c>
+    </row>
+    <row r="1048576" ht="12.75" customHeight="1" s="5"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4198,970 +4499,970 @@
   <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="5">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>isin</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>motivo</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="4">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="5">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>LU2259111008</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Amundi Funds - Emerging Markets Green Bond G EURO Hedged (C)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="5">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>LU0172157363</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>BGF World Mining Euro E</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="5">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>LU0171304552</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>BGF World Energy Euro E</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>LU0329455071</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Candriam Equities L Oncology Impact C EUR</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="4">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="5">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>LU0210534433</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - US Growth A EUR</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="4">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="5">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>LU0210073469</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Europe Dynamic A EUR</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="4">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="5">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>LU0161332480</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Japan Equity A EUR</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="4">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="5">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>LU0210526066</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Pacific Equity A EUR</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="4">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="5">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>LU0210526579</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - China A EUR</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="5">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>LU0333810181</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - India A EUR</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="4">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="5">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>LU0210534516</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Global Select Equity A EUR</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="4">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="5">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>LU0210531934</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Europe High Yield Bond A EUR</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="4">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="5">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>LU0155953517</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Fidelity Funds - European High Yield A EUR</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="4">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="5">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>LU0522351971</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Emerging Markets Debt A EUR Hdg</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="4">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="5">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>LU0210531850</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Global Bond Opportunities A EUR Hdg</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="4">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="5">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>LU0168060498</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Nordea 1 - European Covered Bond BP EUR</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="5">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>FR0010148981</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Carmignac Investissement A EUR Acc</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="4">
-      <c r="A19" s="3" t="n">
+    <row r="19" ht="15" customHeight="1" s="5">
+      <c r="A19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>LU1623762843</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Carmignac Credit A EUR Acc</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>160.020004272461</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="4" t="n">
         <v>159.493</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="4" t="n">
         <v>77.12</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Hang su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="4">
-      <c r="A20" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="5">
+      <c r="A20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>FR0010149302</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Carmignac Emergents A EUR Acc</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
         <v>1650.0419921875</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Hang FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="4">
-      <c r="A21" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="5">
+      <c r="A21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>FR0011269349</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Carmignac Emergents A EUR Ydis</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>215.658996582031</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Hang FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="4">
-      <c r="A22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="5">
+      <c r="A22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>FR0010149120</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Carmignac Sécurité AW Cap EUR</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>1926.78796386719</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="4">
-      <c r="A23" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="5">
+      <c r="A23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>FR0011269083</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Carmignac Sécurité AW EUR Ydis</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Fondi Flessibili</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>99.568000793457</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="4">
-      <c r="A24" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="5">
+      <c r="A24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>LU1163533349</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine E EUR Minc</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>69.37</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="4" t="n">
         <v>68.967</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="4" t="n">
         <v>54.11</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="4">
-      <c r="A25" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="5">
+      <c r="A25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>FR0011269588</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine A EUR Ydis</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Bilanciati</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>128.253005981445</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="4">
-      <c r="A26" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="5">
+      <c r="A26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>LU1163533422</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine A EUR Minc</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>73.19</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="4" t="n">
         <v>72.76049999999999</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="4" t="n">
         <v>54.86</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="4">
-      <c r="A27" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="5">
+      <c r="A27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>FR0010135103</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine A EUR Acc</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Bilanciati</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n">
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>800.525024414063</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="4">
-      <c r="A28" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="5">
+      <c r="A28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>FR0010306142</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine E EUR Acc</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Bilanciati</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>192.75</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="4" t="n">
         <v>191.6865</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="4" t="n">
         <v>57.09</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="4">
-      <c r="A29" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="5">
+      <c r="A29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>LU0336084032</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Carmignac Flexible Bond A EUR Acc</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>1380.40002441406</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="4">
-      <c r="A30" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="5">
+      <c r="A30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>LU0992631050</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Carmignac Flexible Bond A EUR Ydis</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
         <v>1090.80004882813</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="4">
-      <c r="A31" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="5">
+      <c r="A31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>LU1299302684</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Carmignac Flexible Bond A EUR Minc</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
         <v>976.88</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" s="4" t="n">
         <v>977.7005</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="4" t="n">
         <v>38.06</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="4">
-      <c r="A32" s="3" t="n">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="5">
+      <c r="A32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>LU1317704135</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
         <v>178.75</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="4" t="n">
         <v>178.0845</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="4" t="n">
         <v>58.8</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>2026-02-26 19:47</t>
         </is>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="idx" hidden="0" function="0" vbProcedure="0">Fondi!$C$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fondi'!$A$1:$K$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -79,7 +80,10 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -111,6 +115,23 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -363,4127 +384,4625 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="28.23" customWidth="1" style="4" min="2" max="2"/>
-    <col width="54.56" customWidth="1" style="4" min="3" max="3"/>
-    <col width="34.26" customWidth="1" style="4" min="4" max="4"/>
-    <col width="34.11" customWidth="1" style="4" min="5" max="5"/>
+    <col width="28.23" customWidth="1" style="5" min="2" max="2"/>
+    <col width="56.33" customWidth="1" style="5" min="3" max="3"/>
+    <col width="38.09" customWidth="1" style="5" min="4" max="4"/>
+    <col width="50.88" customWidth="1" style="5" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Livello</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Nome Fondo</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Casa Gestione</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Prezzo</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>MM15</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Segnale</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Ultima Modifica</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="5">
-      <c r="A2" s="4" t="n">
+    <row r="2" ht="15" customHeight="1" s="6">
+      <c r="A2" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>LU1548497772</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Allianz Global Artificial Intelligence AT H2-EUR</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Allianz</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="n">
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>296.91</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>289.2315</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>71.08</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="5">
-      <c r="A3" s="4" t="n">
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="6">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>LU0273159177</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>DWS Invest Gold and Precious Metals Equities LC</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>DWS</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
         <v>380.52</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>355.4335</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>69.92</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="5">
-      <c r="A4" s="4" t="n">
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="6">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>LU0273148055</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>DWS Invest Gold and Precious Metals Equities NC</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>DWS</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>325.2</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>303.791</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>70.58</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="5">
-      <c r="A5" s="4" t="n">
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="6">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>LU0208853944</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>JPM Global Natural Resources (EUR) D Acc</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>19.23</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>18.563</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>70.08</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="5">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="6">
+      <c r="A6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>LU0173785626</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Nordea 1 - Swedish Short-Term Bond Fund BP Acc</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Breve Termine</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>20.04</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>20.0695</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>49.53</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="5">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="6">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>LU2357810188</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Amundi S.F. - Diversified Short-Term Bond Select A EUR AD</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Breve Termine</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>51.08</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>51.951</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>6.63</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="5">
-      <c r="A8" s="4" t="n">
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="6">
+      <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>LU1046235815</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Schroder ISF Strategic Credit B EUR Hedged Acc</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Schroders</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Corporate</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>125.72</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>125.6435</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>74.39</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="5">
-      <c r="A9" s="4" t="n">
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="6">
+      <c r="A9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>LU1046236037</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Schroder ISF Strategic Credit A EUR Hedged Inc</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Schroders</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Corporate</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>94.97</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>94.9025</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>78.56</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="5">
-      <c r="A10" s="4" t="n">
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="6">
+      <c r="A10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>IT0004782758</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Eurizon Obbligazioni Euro Breve Term A</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Eurizon</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Euro</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>17.14</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="5" t="n">
         <v>17.1275</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="5" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="5">
-      <c r="A11" s="4" t="n">
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="6">
+      <c r="A11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>LU0430494962</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>JPM Global Short Duration Bond Fund A (acc) EUR hedged</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Breve Termine</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
         <v>7.68</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>7.6755</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>68.19</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="5">
-      <c r="A12" s="4" t="n">
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="6">
+      <c r="A12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>LU0408876448</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>JPM Global Government Short Duration Bond A (acc) EUR</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Governativi</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>10.83</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="5" t="n">
         <v>10.826</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="5" t="n">
         <v>74.66</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="5">
-      <c r="A13" s="4" t="n">
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="6">
+      <c r="A13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>LU1915690595</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Nordea 1 - Active Rates Opportunities Fund BP EUR</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Flessibili</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
         <v>123.11</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="5" t="n">
         <v>122.947</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="5" t="n">
         <v>64.3</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="5">
-      <c r="A14" s="4" t="n">
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="6">
+      <c r="A14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>LU0165520114</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Candriam Bonds Global Inflation Short duration Classic C Acc</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Candriam</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari Inflation Linked</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>149.73</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>149.561</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="5" t="n">
         <v>62.47</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="5">
-      <c r="A15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="6">
+      <c r="A15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>LU1213836080</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Global Technology Fund A-ACC-EUR</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
         <v>58.06</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="5" t="n">
         <v>57.393</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="5" t="n">
         <v>55.14</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="5">
-      <c r="A16" s="4" t="n">
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="6">
+      <c r="A16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>IE000RHGM613</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Nbg Bm Nex Gen Spc Ecy EUR M Acc Unh</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>NBG Asset Management</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Azionari Tematici</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
         <v>22.53</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>22.387</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="5" t="n">
         <v>52.97</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="5">
-      <c r="A17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="6">
+      <c r="A17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>LU2484078832</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Invesco Funds - Invesco Metaverse and AI Fund A Acc EUR</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Invesco</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>18.78</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>18.1005</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="5" t="n">
         <v>55.4</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="5">
-      <c r="A18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="6">
+      <c r="A18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>LU0115773425</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>FF - Global Technology Fund - E - ACC - Euro</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Azionari Tecnologia</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
         <v>73.39</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>72.5565</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="5">
-      <c r="A19" s="4" t="n">
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="6">
+      <c r="A19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>LU1213835942</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Latin America Fund A-ACC-EUR</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Azionari America Latina</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>15.57</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>15.0735</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>72.56999999999999</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="5">
-      <c r="A20" s="4" t="n">
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="6">
+      <c r="A20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>LU0309468808</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Nordea-1 Latin American Eq BP Acc</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Azionari America Latina</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>20.19</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="5" t="n">
         <v>19.8565</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="5" t="n">
         <v>69.73999999999999</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="5">
-      <c r="A21" s="4" t="n">
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="6">
+      <c r="A21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>LU0522352862</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - JPM Latin America Equity D (acc) - EUR</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Azionari America Latina</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>115.37</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>114.5695</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="5" t="n">
         <v>61.47</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="5">
-      <c r="A22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="6">
+      <c r="A22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>LU0326424115</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>BlackRock Global Funds - World Mining Fund A2 EUR Hedged</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>BlackRock</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Azionari Materie Prime</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
         <v>8.48</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="5" t="n">
         <v>7.9335</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="5" t="n">
         <v>55.77</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="5">
-      <c r="A23" s="4" t="n">
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="6">
+      <c r="A23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>LU0106817157</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Schroder ISF Emerg Eur A Acc</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Schroders</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Azionari Europa Emergente</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>32.71</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>32.5935</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="5" t="n">
         <v>57.83</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="5">
-      <c r="A24" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="6">
+      <c r="A24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>LU0326422176</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>BlackRock Global Funds - World Energy Fund A2 EUR Hedged</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>BlackRock</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Azionari Energia</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
         <v>7.57</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>7.2805</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="5" t="n">
         <v>73.44</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="5">
-      <c r="A25" s="4" t="n">
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="6">
+      <c r="A25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>LU0056052961</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Candriam Equities L Emerging Markets C EUR Acc</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Candriam</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Azionari Mercati Emergenti</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>1410.59</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="5" t="n">
         <v>1350.6905</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="5" t="n">
         <v>73.91</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="5">
-      <c r="A26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="6">
+      <c r="A26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>IE00BGMHJH08</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Amundi Alternative Funds II PLC - Amundi Marathon Emerging Markets Bond Fund A EUR Acc</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Azionari Europa/Africa/ME</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>101.24</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="5" t="n">
         <v>33.9061</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" s="5" t="n">
         <v>54.83</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="5">
-      <c r="A27" s="4" t="n">
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="6">
+      <c r="A27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>LU0303816028</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Emerging Europe, Middle East and Africa A Euro</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Azionari Europa/Africa/ME</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>19.32</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="5" t="n">
         <v>18.9775</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" s="5" t="n">
         <v>70.31</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="5">
-      <c r="A28" s="4" t="n">
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="6">
+      <c r="A28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>LU0307839646</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Emerging Markets A Euro</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Azionari Mercati Emergenti</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
         <v>22.65</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="5" t="n">
         <v>21.7815</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="5" t="n">
         <v>81.16</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="5">
-      <c r="A29" s="4" t="n">
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="6">
+      <c r="A29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>LU0114720955</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Global Health Care A EUR</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Azionari Salute/Pharma</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>62.66</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="5" t="n">
         <v>62.26</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" s="5" t="n">
         <v>55.28</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="5">
-      <c r="A30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="6">
+      <c r="A30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>LU0880062913</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Global Healthcare Fund A (acc) - EUR</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Azionari Salute/Pharma</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
         <v>283.65</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>281.0385</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" s="5" t="n">
         <v>50.14</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="5">
-      <c r="A31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="6">
+      <c r="A31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>LU1391767586</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Global Financial Services Fund A-Acc-EUR</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Azionari Finanziari</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>25.14</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>25.655</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="5" t="n">
         <v>35.5</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="5">
-      <c r="A32" s="4" t="n">
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="6">
+      <c r="A32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>LU0210527791</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Europe Equity A EUR</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Azionari Finanziari</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
         <v>32.6199989318848</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>31.8945</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="5" t="n">
         <v>68.95</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="5">
-      <c r="A33" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="6">
+      <c r="A33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>LU0640476718</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Sustainable Consumer Brands A EUR</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Azionari Consumi/Lusso</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n">
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
         <v>72.4459991455078</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="5">
-      <c r="A34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="6">
+      <c r="A34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>LU0069450822</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - America Fund A EUR</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Azionari USA</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>16.07</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="5" t="n">
         <v>15.9835</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" s="5" t="n">
         <v>62.64</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="5">
-      <c r="A35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="6">
+      <c r="A35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>LU1706106447</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Nordea 1 - European Sustainable Stars Equity BP EUR</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n">
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>204.84</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="5" t="n">
         <v>200.7005</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="5" t="n">
         <v>58.56</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="5">
-      <c r="A36" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="6">
+      <c r="A36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>LU0261959422</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - European Dynamic Growth Fund A-Acc-EUR</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
         <v>32.25</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="5" t="n">
         <v>31.87</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I36" s="5" t="n">
         <v>45.48</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="5">
-      <c r="A37" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="6">
+      <c r="A37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>LU0048597586</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - Asia Focus A EUR</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Fidelity</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Azionari Asia Pacifico</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="n">
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>12.5559997558594</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="5">
-      <c r="A38" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="6">
+      <c r="A38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>LU2401078998</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Nordea 1 - Global Sustainable Stars Equity Fund AF EUR</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Nordea</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Azionari Globali</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="n">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
         <v>246.09</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="5" t="n">
         <v>240.2335</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I38" s="5" t="n">
         <v>63.5</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="5">
-      <c r="A39" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="6">
+      <c r="A39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>LU1269890163</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Candriam Bonds Euro High Yield Class C (Q) EUR Dis</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Candriam</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Obbligazionari High Yield</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n">
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
         <v>157.03</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="5" t="n">
         <v>157.212</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" s="5" t="n">
         <v>36.64</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="5">
-      <c r="A40" s="4" t="n">
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="6">
+      <c r="A40" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>FR0010510800</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Amundi Fds - Euro Government Bond A EUR C</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Monetari Euro</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
         <v>113.161003112793</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="5" t="n">
         <v>113.0768</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="5" t="n">
         <v>70.62</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="5">
-      <c r="A41" s="4" t="n">
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="6">
+      <c r="A41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>LU0568621618</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Euro Government Liquidity A EUR</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>JPMorgan</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Monetari Euro</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n">
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>128.860000610352</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="5" t="n">
         <v>128.617</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="5">
-      <c r="A42" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="6">
+      <c r="A42" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>LU0987184941</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Absolute Return Forex R EUR (C)</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Fondi Flessibili</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
         <v>103.65</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="5" t="n">
         <v>103.392</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="I42" s="5" t="n">
         <v>76.47</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="5">
-      <c r="A43" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="6">
+      <c r="A43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>LU0557854147</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Asia Equity Focus A EUR (C)</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Azionari Pacifico</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="n">
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>232.15</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="5" t="n">
         <v>219.028</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I43" s="5" t="n">
         <v>73.76000000000001</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="5">
-      <c r="A44" s="4" t="n">
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="6">
+      <c r="A44" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>LU0568620560</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Amundi F. Cash EUR A2 EUR</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Fondi di Mercato Monetario Euro</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="n">
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>106.15</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="5" t="n">
         <v>106.1105</v>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="I44" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="5">
-      <c r="A45" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="6">
+      <c r="A45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>LU2386146430</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Emerging Markets Equity Select A2 EUR (C)</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="n">
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>84.08</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="5" t="n">
         <v>79.8175</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="I45" s="5" t="n">
         <v>70.97</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="5">
-      <c r="A46" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="6">
+      <c r="A46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>LU0568583420</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Equity Japan Target A EUR (C)</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Azionari Paese</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="n">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
         <v>329.51</v>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H46" s="5" t="n">
         <v>316.654</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="I46" s="5" t="n">
         <v>67.95999999999999</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="5">
-      <c r="A47" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="6">
+      <c r="A47" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>LU0616241476</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Euro Aggregate Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Obb. Altre Special.</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n">
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
         <v>134.6</v>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="5" t="n">
         <v>133.8405</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="I47" s="5" t="n">
         <v>88.51000000000001</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="5">
-      <c r="A48" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="6">
+      <c r="A48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>LU0518421895</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Euro Government Bond Responsible A EUR (C)</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Obb. Euro Governativi M/L Termine</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="n">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
         <v>125.16</v>
       </c>
-      <c r="H48" s="4" t="n">
+      <c r="H48" s="5" t="n">
         <v>124.201</v>
       </c>
-      <c r="I48" s="4" t="n">
+      <c r="I48" s="5" t="n">
         <v>87.31</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="5">
-      <c r="A49" s="4" t="n">
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="6">
+      <c r="A49" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>LU1883303551</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Euroland Equity A CHF Hgd (C)</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Azionari Area Euro</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="n">
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
         <v>111.459999084473</v>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H49" s="5" t="n">
         <v>109.2185</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I49" s="5" t="n">
         <v>68.13</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="5">
-      <c r="A50" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="6">
+      <c r="A50" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>LU0568607203</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Euroland Equity Small Cap Select A EUR (C)</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Azionari Area Euro</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="n">
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
         <v>260.57</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="5" t="n">
         <v>256.88</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="I50" s="5" t="n">
         <v>55.18</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="5">
-      <c r="A51" s="4" t="n">
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="6">
+      <c r="A51" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>LU1883310846</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Europe Equity Income Select A2 AUD H QTI D</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="n">
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
         <v>56.060001373291</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="5" t="n">
         <v>55.1783</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="I51" s="5" t="n">
         <v>68.39</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="5">
-      <c r="A52" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="6">
+      <c r="A52" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>LU1883306497</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - European Equity Small Cap A EUR (C)</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="n">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
         <v>222.52</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="5" t="n">
         <v>221.319</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="I52" s="5" t="n">
         <v>51.08</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="5">
-      <c r="A53" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="6">
+      <c r="A53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>LU3081003082</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Absolute Return Global Opportunities Bond A EUR MTD D</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Obb. Altre Special.</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="n">
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
         <v>50.47</v>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="H53" s="5" t="n">
         <v>50.3505</v>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="I53" s="5" t="n">
         <v>59.83</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="5">
-      <c r="A54" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="6">
+      <c r="A54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>LU2330497517</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Corporate Bond Select A2 EUR Hedged Acc</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Obb. Intern. Corporate Investment Grade</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="n">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
         <v>46.93</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="5" t="n">
         <v>46.734</v>
       </c>
-      <c r="I54" s="4" t="n">
+      <c r="I54" s="5" t="n">
         <v>79.70999999999999</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="5">
-      <c r="A55" s="4" t="n">
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="6">
+      <c r="A55" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>LU2531474588</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds Global Equity Climate A USD Capitalisation</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Azionari Internazionali</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="n">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
         <v>87.5500030517578</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="5" t="n">
         <v>87.523</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="I55" s="5" t="n">
         <v>57.17</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="5">
-      <c r="A56" s="4" t="n">
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="6">
+      <c r="A56" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>LU1883318666</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Equity Responsible A CHF (C)</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Azionari Altri Settori</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="n">
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
         <v>484.470001220703</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H56" s="5" t="n">
         <v>477.475</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="I56" s="5" t="n">
         <v>62.67</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="5">
-      <c r="A57" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="6">
+      <c r="A57" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>LU1162499526</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Global High Yield Bond A EUR Hgd (C)</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Obb. Dollaro High Yield</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="n">
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
         <v>114.15</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="5" t="n">
         <v>113.925</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I57" s="5" t="n">
         <v>58.25</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="5">
-      <c r="A58" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="6">
+      <c r="A58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>LU0442405998</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Inflation Short Duration Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Obb. Intern. Governativi</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="n">
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
         <v>105.21</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="5" t="n">
         <v>105.189</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="I58" s="5" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="5">
-      <c r="A59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="6">
+      <c r="A59" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>LU1883327907</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Multi-Asset A USD (C)</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Bilanciati Obbligazionari</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="n">
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
         <v>170.660003662109</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="5" t="n">
         <v>169.8945</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="I59" s="5" t="n">
         <v>57.58</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="5">
-      <c r="A60" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="6">
+      <c r="A60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>LU1883334275</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Global Subordinated Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Obb. Altre Special.</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="n">
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
         <v>75.26000000000001</v>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="5" t="n">
         <v>75.00149999999999</v>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="I60" s="5" t="n">
         <v>96.48999999999999</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="5">
-      <c r="A61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="6">
+      <c r="A61" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>LU0945151578</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Impact Euro Corporate Short Term Green Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Obb. Euro Corporate Investment Grade</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="n">
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
         <v>105.99</v>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H61" s="5" t="n">
         <v>105.9255</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="I61" s="5" t="n">
         <v>81.06</v>
       </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="5">
-      <c r="A62" s="4" t="n">
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="6">
+      <c r="A62" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>LU2585853059</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Income Opportunities A2 AUD H MTD3 (D)</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Fondi Flessibili</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="n">
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
         <v>56.4099998474121</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H62" s="5" t="n">
         <v>56.2893</v>
       </c>
-      <c r="I62" s="4" t="n">
+      <c r="I62" s="5" t="n">
         <v>64.94</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="5">
-      <c r="A63" s="4" t="n">
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="6">
+      <c r="A63" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>LU1923161894</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Japan Equity Select A USD (C)</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Azionari Pacifico</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="n">
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
         <v>80.620002746582</v>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="5" t="n">
         <v>77.80200000000001</v>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="I63" s="5" t="n">
         <v>63.81</v>
       </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="5">
-      <c r="A64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="6">
+      <c r="A64" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>LU0552029406</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Latin America Equity A EUR (C)</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="n">
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
         <v>128.36</v>
       </c>
-      <c r="H64" s="4" t="n">
+      <c r="H64" s="5" t="n">
         <v>123.431</v>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="I64" s="5" t="n">
         <v>62.06</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="5">
-      <c r="A65" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="6">
+      <c r="A65" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>LU1883336569</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Optimal Yield A EUR (C)</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Obb. Flessibili</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="n">
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
         <v>118.01</v>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="5" t="n">
         <v>117.8</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="I65" s="5" t="n">
         <v>71.58</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="5">
-      <c r="A66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="6">
+      <c r="A66" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>LU1883339233</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Optimal Yield Short Term A EUR (C)</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Obb. Flessibili</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="n">
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
         <v>58.78</v>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H66" s="5" t="n">
         <v>58.682</v>
       </c>
-      <c r="I66" s="4" t="n">
+      <c r="I66" s="5" t="n">
         <v>71.15000000000001</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="5">
-      <c r="A67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="6">
+      <c r="A67" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>LU1880401101</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - US Bond A EUR (C)</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Obb. Dollaro Governativi M/L Termine</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="n">
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
         <v>53.03</v>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="5" t="n">
         <v>52.463</v>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="I67" s="5" t="n">
         <v>69.03</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="5">
-      <c r="A68" s="4" t="n">
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="6">
+      <c r="A68" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>LU2559893917</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - US Corporate Bond Climate A USD (C)</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="n">
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
         <v>58.0699996948242</v>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="H68" s="5" t="n">
         <v>57.7105</v>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="I68" s="5" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="5">
-      <c r="A69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="6">
+      <c r="A69" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>LU3238210200</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - US Corporate Bond Select A EUR Hgd AD (D)</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Obb. Dollaro Corporate Investment Grade</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="n">
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
         <v>50.6</v>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="H69" s="5" t="n">
         <v>50.331</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="I69" s="5" t="n">
         <v>77.36</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="5">
-      <c r="A70" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="6">
+      <c r="A70" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>LU1883854199</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - US Equity Fundamental Growth A EUR C</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Azionari America</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="n">
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
         <v>562.75</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="5" t="n">
         <v>567.1135</v>
       </c>
-      <c r="I70" s="4" t="n">
+      <c r="I70" s="5" t="n">
         <v>30.23</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="5">
-      <c r="A71" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="6">
+      <c r="A71" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>LU1883859230</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - US Equity Research A EUR (C)</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>Azionari America</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="n">
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
         <v>24.59</v>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="5" t="n">
         <v>23.984</v>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="I71" s="5" t="n">
         <v>54.93</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="5">
-      <c r="A72" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="6">
+      <c r="A72" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>LU2146567529</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - US Equity Select A EUR (C)</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Amundi</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Azionari America</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="n">
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
         <v>81.53</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="H72" s="5" t="n">
         <v>81.0485</v>
       </c>
-      <c r="I72" s="4" t="n">
+      <c r="I72" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="5">
-      <c r="A73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="6">
+      <c r="A73" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>FR0010312660</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Carmignac Investissement E EUR Acc</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="n">
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n">
         <v>355.64</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="5" t="n">
         <v>348.33</v>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="I73" s="5" t="n">
         <v>61.47</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="5">
-      <c r="A74" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="6">
+      <c r="A74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>LU0336083810</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Carmignac Asia Discovery A EUR Acc EUR</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="n">
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
         <v>2717.27099609375</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="5">
-      <c r="A75" s="4" t="n">
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="6">
+      <c r="A75" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>FR0011269182</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Carmignac Investissement A EUR Ydis</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Azionari Internazionali</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="n">
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
         <v>279.91</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="5" t="n">
         <v>278.601</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="I75" s="5" t="n">
         <v>47.36</v>
       </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="5">
-      <c r="A76" s="4" t="n">
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="6">
+      <c r="A76" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>LU1317704051</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Carmignac Long-Short Europ. Eqs A EUR Acc</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="n">
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
         <v>190.63</v>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="5" t="n">
         <v>189.8945</v>
       </c>
-      <c r="I76" s="4" t="n">
+      <c r="I76" s="5" t="n">
         <v>59.29</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K76" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="5">
-      <c r="A77" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="6">
+      <c r="A77" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>LU1861216783</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>BGF Next Generation Technology E2 Cap EUR Hdg</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Blackrock Global Funds SICAV</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>Azionari Altri Settori</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="n">
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
         <v>21.24</v>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="5">
-      <c r="A78" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
+    <row r="78" ht="15" customHeight="1" s="6">
+      <c r="A78" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>LU0705071453</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>RAM (Lux) SF European Market Neutral Eq.B EUR</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>RAM (Lux) Systematic Funds</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="n">
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="n">
         <v>184.09</v>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="5">
-      <c r="A79" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="6">
+      <c r="A79" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>LU1176912761</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>JPM Europe Eq. Absolute Alpha D (perf) Acc EUR</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>JP Morgan Funds SICAV</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>Azionari Europa</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="n">
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="n">
         <v>155.39</v>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="5">
-      <c r="A80" t="n">
-        <v>3</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
+    <row r="80" ht="15" customHeight="1" s="6">
+      <c r="A80" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>IE00B79S1F56</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>Pimco Commodities Plus Strategy Fund Classe E Eur Hdg</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Pimco Funds Global Investors Series PLC</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="n">
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
         <v>8.74</v>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="5">
-      <c r="A81" t="n">
-        <v>3</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
+    <row r="81" ht="15" customHeight="1" s="6">
+      <c r="A81" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>LU1106545376</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>Vontobel Fund - Non-Food Commodity Classe H EUR Acc</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Vontobel Fund SICAV</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="n">
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
         <v>100.46</v>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="5">
-      <c r="A82" t="n">
-        <v>3</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
+    <row r="82" ht="15" customHeight="1" s="6">
+      <c r="A82" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>AT0000688684</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>Raiffeisen Azionario Energia (r)</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Raiffeisen Kapitalanlage Gesellschaft</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>Azionari Settoriali - Energia</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="n">
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
         <v>220.12</v>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="5">
-      <c r="A83" t="n">
-        <v>3</v>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
+    <row r="83" ht="15" customHeight="1" s="6">
+      <c r="A83" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>LU0757427116</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>Threadneedle (Lux) - Enhanced Commodities Fund Classe AU EUR</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Columbia Threadneedle (Lux) I</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>Ritorno Assoluto Materie Prime</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="n">
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
         <v>16.23</v>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="5">
-      <c r="A84" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
+    <row r="84" ht="15" customHeight="1" s="6">
+      <c r="A84" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>LU0273974336</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>Amundi S.F. - EUR Commodities Classe F EUR Acc</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Amundi SF SICAV</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>Ritorno Assoluto Materie Prime</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="n">
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
         <v>2.75</v>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="5">
-      <c r="A85" t="n">
-        <v>3</v>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
+    <row r="85" ht="15" customHeight="1" s="6">
+      <c r="A85" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>LU0173784223</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Nordea 1 - Norwegian Equity Fund Classe BP Eur</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Nordea 1 SICAV</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>Azionari Norvegia</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="n">
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
         <v>44.82</v>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="5">
-      <c r="A86" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
+    <row r="86" ht="15" customHeight="1" s="6">
+      <c r="A86" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>LU0173770354</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Nordea 1 - Norwegian Equity Fund Classe E Eur (acc)</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Nordea 1 SICAV</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Azionari Norvegia</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="n">
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
         <v>38.1</v>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="5">
-      <c r="A87" t="n">
-        <v>3</v>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
+    <row r="87" ht="15" customHeight="1" s="6">
+      <c r="A87" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>IE00BLLXH031</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>Neu.Berman 5G Connectivity Classe M Eur Acc</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Neuberger Berman Europe</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Azionari Settoriali - Telecomunicazioni</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="n">
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n">
         <v>20.84</v>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="5">
-      <c r="A88" t="n">
-        <v>3</v>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
+    <row r="88" ht="15" customHeight="1" s="6">
+      <c r="A88" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>LU1881514001</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>FF - Future Connectivity Fund Classe A EUR Acc</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Fidelity Funds SICAV</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Azionari Settoriali - Telecomunicazioni</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="n">
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
         <v>20.74</v>
       </c>
     </row>
-    <row r="1048576" ht="12.75" customHeight="1" s="5"/>
+    <row r="89" ht="15" customHeight="1" s="6">
+      <c r="A89" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>LU0078277505</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Templeton Eastern Europe Fund Classe A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Franklin Templeton Investment Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Europa Orientale</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>22.43</v>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="6">
+      <c r="A90" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>IE00B23S7K36</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Bny Mellon Brazil Equity Fund Classe A</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>BNY Mellon Global Funds PLC</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Brasile</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="6">
+      <c r="A91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>LU2145463613</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Robeco - Smart Materials Equities Classe D Eur</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Materie Prime e Chimiche</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Materie Prime e Chimiche</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>504.31</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="6">
+      <c r="A92" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>LU0301637293</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>JPMorgan Funds - Korea Equity Fund Classe A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>JP Morgan Funds SICAV</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Korea</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>28.24</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="6">
+      <c r="A93" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>IT0001021192</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Eurizon Azioni Italia</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Eurizon Capital SGR</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Italia - Large &amp; Mid Cap Value</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>44.18</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="6">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>LU1861217831</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>BGF FinTech Fund Classe E2 EUR Hedged Acc</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Blackrock Global Funds SICAV</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Fintech EUR Hedged</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="6">
+      <c r="A95" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>LU2387455517</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Franklin Intelligent Machines Fund - Classe N Eur Acc</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Franklin Templeton Investment Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Intelligenza Artificiale (Globale)</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>17.89</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="6">
+      <c r="A96" t="n">
+        <v>3</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>LU1548497699</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Allianz GIF - Global Artificial Intelligence Classe AT Eur</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Intelligenza Artificiale (Globale)</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="n">
+        <v>346.08</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="6">
+      <c r="A97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>LU0604766674</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Allianz Global Metals and Mining Classe AT EUR Acc</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Metalli e Minerali</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>123.31</v>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="6">
+      <c r="A98" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>LU0284993374</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Lemanik Sicav High Growth Cap Retail Eur</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Lemanik SICAV</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Italia - Large &amp; Mid Cap</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="n">
+        <v>468.6</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="6">
+      <c r="A99" t="n">
+        <v>3</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>IE00BWY56V74</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Algebris Financial Equity Fund Classe R EUR (Acc)</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Algebris Financial Equity Fund</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Finanza (Globale)</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="n">
+        <v>289.2</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="6">
+      <c r="A100" t="n">
+        <v>3</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>LU0757431738</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Threadneedle (Lux) - Global Technology Fund Classe DU EUR</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Columbia Threadneedle (Lux) I</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Informatica e Tecnologia</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="n">
+        <v>269.07</v>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="6">
+      <c r="A101" t="n">
+        <v>3</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>LU0572952280</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Janus Henderson Horizon Fund - Global Technology Fund Eur Classe A</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Janus Henderson Horizon Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Settoriali - Informatica e Tecnologia</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="n">
+        <v>257.18</v>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="6">
+      <c r="A102" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>LU0073229840</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Morgan Stanley Emerging Markets Equity Fund Classe A EUR Acc</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Morgan Stanley Investment Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Globali (Mercati Emergenti) - Large &amp; Mid Cap Growth</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="n">
+        <v>62.97</v>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="6">
+      <c r="A103" t="n">
+        <v>3</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>LU0300834669</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Alken Fund - Small Cap Europe Eur Classe R</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Alken Fund SICAV</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Azionari Europa (Mercati Sviluppati) - Small Cap</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="n">
+        <v>607.48</v>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="6"/>
+    <row r="1048575" ht="12.75" customHeight="1" s="6"/>
+    <row r="1048576" ht="12.8" customHeight="1" s="6"/>
   </sheetData>
+  <autoFilter ref="A1:K88"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4499,970 +5018,970 @@
   <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>isin</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>motivo</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="5">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="6">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>LU2259111008</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Amundi Funds - Emerging Markets Green Bond G EURO Hedged (C)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="6">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>LU0172157363</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>BGF World Mining Euro E</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="6">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>LU0171304552</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>BGF World Energy Euro E</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="6">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>LU0329455071</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Candriam Equities L Oncology Impact C EUR</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>LU0210534433</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - US Growth A EUR</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="6">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>LU0210073469</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Europe Dynamic A EUR</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="6">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>LU0161332480</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Japan Equity A EUR</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="6">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>LU0210526066</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Pacific Equity A EUR</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="6">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>LU0210526579</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - China A EUR</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="6">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>LU0333810181</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - India A EUR</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="6">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>LU0210534516</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Global Select Equity A EUR</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="5">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="6">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>LU0210531934</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Europe High Yield Bond A EUR</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="6">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>LU0155953517</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Fidelity Funds - European High Yield A EUR</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="6">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>LU0522351971</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Emerging Markets Debt A EUR Hdg</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="6">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>LU0210531850</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>JPMorgan Funds - Global Bond Opportunities A EUR Hdg</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="6">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>LU0168060498</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Nordea 1 - European Covered Bond BP EUR</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="6">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>FR0010148981</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Carmignac Investissement A EUR Acc</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Nessun prezzo su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5">
-      <c r="A19" s="4" t="n">
+    <row r="19" ht="15" customHeight="1" s="6">
+      <c r="A19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>LU1623762843</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Carmignac Credit A EUR Acc</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>160.020004272461</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>159.493</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>77.12</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Hang su FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="5">
-      <c r="A20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="6">
+      <c r="A20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>FR0010149302</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Carmignac Emergents A EUR Acc</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>1650.0419921875</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Hang FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="5">
-      <c r="A21" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="6">
+      <c r="A21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>FR0011269349</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Carmignac Emergents A EUR Ydis</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Azionari Paesi Emergenti</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>215.658996582031</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Hang FT Markets</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="5">
-      <c r="A22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="6">
+      <c r="A22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>FR0010149120</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Carmignac Sécurité AW Cap EUR</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
         <v>1926.78796386719</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="5">
-      <c r="A23" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="6">
+      <c r="A23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>FR0011269083</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Carmignac Sécurité AW EUR Ydis</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Fondi Flessibili</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>99.568000793457</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="5">
-      <c r="A24" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="6">
+      <c r="A24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>LU1163533349</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine E EUR Minc</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
         <v>69.37</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>68.967</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="5" t="n">
         <v>54.11</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="5">
-      <c r="A25" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="6">
+      <c r="A25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>FR0011269588</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine A EUR Ydis</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Bilanciati</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>128.253005981445</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="5">
-      <c r="A26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="6">
+      <c r="A26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>LU1163533422</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine A EUR Minc</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>73.19</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="5" t="n">
         <v>72.76049999999999</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" s="5" t="n">
         <v>54.86</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="5">
-      <c r="A27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="6">
+      <c r="A27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>FR0010135103</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine A EUR Acc</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Bilanciati</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>800.525024414063</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="5">
-      <c r="A28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="6">
+      <c r="A28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>FR0010306142</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Carmignac Patrimoine E EUR Acc</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Bilanciati</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
         <v>192.75</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="5" t="n">
         <v>191.6865</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="5" t="n">
         <v>57.09</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="5">
-      <c r="A29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="6">
+      <c r="A29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>LU0336084032</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Carmignac Flexible Bond A EUR Acc</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>1380.40002441406</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="5">
-      <c r="A30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="6">
+      <c r="A30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>LU0992631050</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Carmignac Flexible Bond A EUR Ydis</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
         <v>1090.80004882813</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="5">
-      <c r="A31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="6">
+      <c r="A31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>LU1299302684</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Carmignac Flexible Bond A EUR Minc</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Obb. Misti</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>976.88</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>977.7005</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="5" t="n">
         <v>38.06</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-26 19:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="5">
-      <c r="A32" s="4" t="n">
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="6">
+      <c r="A32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>LU1317704135</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Carmignac Long-Short Europ. Eqs E EUR Acc</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Carmignac</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Altri</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
         <v>178.75</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>178.0845</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="5" t="n">
         <v>58.8</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>2026-02-26 19:47</t>
         </is>

--- a/fondi_monitoraggio.xlsx
+++ b/fondi_monitoraggio.xlsx
@@ -384,7 +384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28.23" customWidth="1" style="5" min="2" max="2"/>
@@ -4504,7 +4504,7 @@
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="6">
-      <c r="A89" t="n">
+      <c r="A89" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B89" s="8" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="6">
-      <c r="A90" t="n">
+      <c r="A90" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="6">
-      <c r="A91" t="n">
+      <c r="A91" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="6">
-      <c r="A92" t="n">
+      <c r="A92" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="6">
-      <c r="A93" t="n">
+      <c r="A93" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="6">
-      <c r="A94" t="n">
+      <c r="A94" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="6">
-      <c r="A95" t="n">
+      <c r="A95" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B95" s="8" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="6">
-      <c r="A96" t="n">
+      <c r="A96" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="6">
-      <c r="A97" t="n">
+      <c r="A97" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="6">
-      <c r="A98" t="n">
+      <c r="A98" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="6">
-      <c r="A99" t="n">
+      <c r="A99" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="6">
-      <c r="A100" t="n">
+      <c r="A100" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="6">
-      <c r="A101" t="n">
+      <c r="A101" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -4933,27 +4933,27 @@
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="6">
-      <c r="A102" t="n">
+      <c r="A102" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>LU0073229840</t>
+          <t>LU0300834669</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Morgan Stanley Emerging Markets Equity Fund Classe A EUR Acc</t>
+          <t>Alken Fund - Small Cap Europe Eur Classe R</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Morgan Stanley Investment Fund SICAV</t>
+          <t>Alken Fund SICAV</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Azionari Globali (Mercati Emergenti) - Large &amp; Mid Cap Growth</t>
+          <t>Azionari Europa (Mercati Sviluppati) - Small Cap</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -4962,42 +4962,10 @@
         </is>
       </c>
       <c r="G102" s="8" t="n">
-        <v>62.97</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="6">
-      <c r="A103" t="n">
-        <v>3</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>LU0300834669</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>Alken Fund - Small Cap Europe Eur Classe R</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>Alken Fund SICAV</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>Azionari Europa (Mercati Sviluppati) - Small Cap</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="n">
         <v>607.48</v>
       </c>
     </row>
+    <row r="103" ht="15" customHeight="1" s="6"/>
     <row r="104" ht="15" customHeight="1" s="6"/>
     <row r="1048575" ht="12.75" customHeight="1" s="6"/>
     <row r="1048576" ht="12.8" customHeight="1" s="6"/>
